--- a/Versão5/ABNT/Ontologia_NBR15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1S.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5651B4A-919C-45CD-A4CA-21C845F81C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814B19DC-B791-49AF-B906-DDD54CEF0F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7945" uniqueCount="867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7945" uniqueCount="868">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2661,12 +2661,6 @@
     <t>NBR.Temáticas</t>
   </si>
   <si>
-    <t>[ OST_Materials ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ IfcMaterial ] </t>
-  </si>
-  <si>
     <t>[ - ]</t>
   </si>
   <si>
@@ -2682,16 +2676,25 @@
     <t>[ OST_Rooms : OST_MEPSpaces : OST_MEPSystemZone ]</t>
   </si>
   <si>
-    <t>[ IfcSpace ]</t>
-  </si>
-  <si>
-    <t>[ IfcProperty ]</t>
-  </si>
-  <si>
     <t>[ OST_Sheets : OST_TitleBlocks : OST_Revisions : OST_RevisionNumberingSequences ]</t>
   </si>
   <si>
     <t>[ IfcAnnotation ]</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_MaterialTags ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial : IfcText : IfcLabel : IfcMaterialRelationship ]</t>
+  </si>
+  <si>
+    <t>[ BuiltInParameter ]</t>
+  </si>
+  <si>
+    <t>[ IfcProperty : IfcIdentifier : IfcText ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
   </si>
 </sst>
 </file>
@@ -3235,7 +3238,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{75D7255F-4B16-4C61-A12B-6DBA4ACA1970}"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="21">
     <dxf>
       <font>
         <b val="0"/>
@@ -3355,6 +3358,13 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -3745,14 +3755,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CFA2BD-3953-447B-BF8D-35BA528839AD}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -3763,7 +3773,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>307</v>
       </c>
@@ -3774,7 +3784,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>308</v>
       </c>
@@ -3785,7 +3795,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -3796,7 +3806,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -3808,7 +3818,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -3820,7 +3830,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -3831,7 +3841,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="36" t="s">
         <v>9</v>
       </c>
@@ -3842,7 +3852,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>309</v>
       </c>
@@ -3853,7 +3863,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>311</v>
       </c>
@@ -3864,7 +3874,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>312</v>
       </c>
@@ -3875,7 +3885,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -3886,7 +3896,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>313</v>
       </c>
@@ -3897,7 +3907,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>314</v>
       </c>
@@ -3908,7 +3918,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>315</v>
       </c>
@@ -3919,7 +3929,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>316</v>
       </c>
@@ -3930,7 +3940,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -3941,19 +3951,19 @@
         <v>689</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>317</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46244.501170138887</v>
+        <v>46249.322863657406</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>698</v>
       </c>
@@ -3964,7 +3974,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="36" t="s">
         <v>692</v>
       </c>
@@ -3976,7 +3986,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>699</v>
       </c>
@@ -3988,7 +3998,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>306</v>
       </c>
@@ -3999,7 +4009,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>318</v>
       </c>
@@ -4010,7 +4020,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>324</v>
       </c>
@@ -4021,7 +4031,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>326</v>
       </c>
@@ -4032,7 +4042,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="36" t="s">
         <v>685</v>
       </c>
@@ -4043,7 +4053,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="36" t="s">
         <v>827</v>
       </c>
@@ -4054,7 +4064,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="36" t="s">
         <v>829</v>
       </c>
@@ -4065,7 +4075,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="36" t="s">
         <v>831</v>
       </c>
@@ -4076,7 +4086,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="36" t="s">
         <v>833</v>
       </c>
@@ -4087,7 +4097,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="36" t="s">
         <v>835</v>
       </c>
@@ -4098,7 +4108,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="36" t="s">
         <v>837</v>
       </c>
@@ -4109,7 +4119,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="36" t="s">
         <v>839</v>
       </c>
@@ -4120,7 +4130,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="36" t="s">
         <v>841</v>
       </c>
@@ -4131,7 +4141,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="36" t="s">
         <v>843</v>
       </c>
@@ -4142,7 +4152,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="36" t="s">
         <v>845</v>
       </c>
@@ -4153,7 +4163,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="36" t="s">
         <v>847</v>
       </c>
@@ -4164,7 +4174,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>849</v>
       </c>
@@ -4175,7 +4185,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="62" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="62" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="36" t="s">
         <v>851</v>
       </c>
@@ -4202,34 +4212,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6EEAB6-D26C-4450-83AD-F740CF51FA1E}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.83203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="56.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.1640625" customWidth="1"/>
-    <col min="27" max="27" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.09765625" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.8984375" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.296875" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.3984375" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.3984375" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="62.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="65" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.796875" style="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="45.59765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="35.69921875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.296875" customWidth="1"/>
+    <col min="27" max="27" width="57.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>637</v>
       </c>
@@ -4312,7 +4322,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46">
         <v>2</v>
       </c>
@@ -4391,10 +4401,10 @@
         <v>Key-ABNT-2</v>
       </c>
       <c r="X2" s="35" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="Y2" s="35" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="Z2" s="35" t="s">
         <v>706</v>
@@ -4403,7 +4413,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="46">
         <v>3</v>
       </c>
@@ -4482,10 +4492,10 @@
         <v>Key-ABNT-3</v>
       </c>
       <c r="X3" s="35" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="Y3" s="35" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="Z3" s="35" t="s">
         <v>707</v>
@@ -4494,7 +4504,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="46">
         <v>4</v>
       </c>
@@ -4573,10 +4583,10 @@
         <v>Key-ABNT-4</v>
       </c>
       <c r="X4" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y4" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z4" s="35" t="s">
         <v>708</v>
@@ -4585,7 +4595,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="46">
         <v>5</v>
       </c>
@@ -4664,10 +4674,10 @@
         <v>Key-ABNT-5</v>
       </c>
       <c r="X5" s="35" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="Y5" s="35" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="Z5" s="35" t="s">
         <v>709</v>
@@ -4676,7 +4686,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="46">
         <v>6</v>
       </c>
@@ -4755,10 +4765,10 @@
         <v>Key-ABNT-6</v>
       </c>
       <c r="X6" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y6" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z6" s="35" t="s">
         <v>624</v>
@@ -4767,7 +4777,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="46">
         <v>7</v>
       </c>
@@ -4846,10 +4856,10 @@
         <v>Key-ABNT-7</v>
       </c>
       <c r="X7" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y7" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Z7" s="35" t="s">
         <v>710</v>
@@ -4858,7 +4868,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="46">
         <v>8</v>
       </c>
@@ -4937,10 +4947,10 @@
         <v>Key-ABNT-8</v>
       </c>
       <c r="X8" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y8" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Z8" s="35" t="s">
         <v>711</v>
@@ -4949,7 +4959,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
         <v>9</v>
       </c>
@@ -5028,10 +5038,10 @@
         <v>Key-ABNT-9</v>
       </c>
       <c r="X9" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y9" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Z9" s="35" t="s">
         <v>712</v>
@@ -5040,7 +5050,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="46">
         <v>10</v>
       </c>
@@ -5119,10 +5129,10 @@
         <v>Key-ABNT-10</v>
       </c>
       <c r="X10" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y10" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Z10" s="35" t="s">
         <v>713</v>
@@ -5131,7 +5141,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="46">
         <v>11</v>
       </c>
@@ -5210,10 +5220,10 @@
         <v>Key-ABNT-11</v>
       </c>
       <c r="X11" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y11" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Z11" s="35" t="s">
         <v>714</v>
@@ -5222,7 +5232,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="46">
         <v>12</v>
       </c>
@@ -5301,10 +5311,10 @@
         <v>Key-ABNT-12</v>
       </c>
       <c r="X12" s="35" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="Y12" s="35" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="Z12" s="35" t="s">
         <v>715</v>
@@ -5313,7 +5323,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="46">
         <v>13</v>
       </c>
@@ -5392,10 +5402,10 @@
         <v>Key-ABNT-13</v>
       </c>
       <c r="X13" s="35" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="Y13" s="35" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="Z13" s="35" t="s">
         <v>716</v>
@@ -5404,7 +5414,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="46">
         <v>14</v>
       </c>
@@ -5483,10 +5493,10 @@
         <v>Key-ABNT-14</v>
       </c>
       <c r="X14" s="63" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="Y14" s="64" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="Z14" s="35" t="s">
         <v>717</v>
@@ -5495,7 +5505,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="46">
         <v>15</v>
       </c>
@@ -5575,10 +5585,10 @@
         <v>Key-ABNT-15</v>
       </c>
       <c r="X15" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y15" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z15" s="50" t="s">
         <v>746</v>
@@ -5588,7 +5598,7 @@
         <v>Transactional services</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="46">
         <v>16</v>
       </c>
@@ -5668,10 +5678,10 @@
         <v>Key-ABNT-16</v>
       </c>
       <c r="X16" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y16" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z16" s="50" t="s">
         <v>747</v>
@@ -5681,7 +5691,7 @@
         <v>Administrative services</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="46">
         <v>17</v>
       </c>
@@ -5761,10 +5771,10 @@
         <v>Key-ABNT-17</v>
       </c>
       <c r="X17" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y17" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z17" s="50" t="s">
         <v>761</v>
@@ -5774,7 +5784,7 @@
         <v>Communication Services</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="46">
         <v>18</v>
       </c>
@@ -5854,10 +5864,10 @@
         <v>Key-ABNT-18</v>
       </c>
       <c r="X18" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y18" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z18" s="50" t="s">
         <v>762</v>
@@ -5867,7 +5877,7 @@
         <v>Conceptualization Services</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="46">
         <v>19</v>
       </c>
@@ -5947,10 +5957,10 @@
         <v>Key-ABNT-19</v>
       </c>
       <c r="X19" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y19" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z19" s="50" t="s">
         <v>765</v>
@@ -5960,7 +5970,7 @@
         <v>Information services</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="46">
         <v>20</v>
       </c>
@@ -6040,10 +6050,10 @@
         <v>Key-ABNT-20</v>
       </c>
       <c r="X20" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y20" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z20" s="50" t="s">
         <v>766</v>
@@ -6053,7 +6063,7 @@
         <v>Organization Services</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="46">
         <v>21</v>
       </c>
@@ -6133,10 +6143,10 @@
         <v>Key-ABNT-21</v>
       </c>
       <c r="X21" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y21" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z21" s="50" t="s">
         <v>763</v>
@@ -6146,7 +6156,7 @@
         <v>Project Development Services</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="46">
         <v>22</v>
       </c>
@@ -6226,10 +6236,10 @@
         <v>Key-ABNT-22</v>
       </c>
       <c r="X22" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y22" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z22" s="50" t="s">
         <v>764</v>
@@ -6239,7 +6249,7 @@
         <v>Document Services</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="46">
         <v>23</v>
       </c>
@@ -6319,10 +6329,10 @@
         <v>Key-ABNT-23</v>
       </c>
       <c r="X23" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y23" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z23" s="50" t="s">
         <v>767</v>
@@ -6332,7 +6342,7 @@
         <v>Implementation Services</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="46">
         <v>24</v>
       </c>
@@ -6412,10 +6422,10 @@
         <v>Key-ABNT-24</v>
       </c>
       <c r="X24" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y24" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z24" s="50" t="s">
         <v>768</v>
@@ -6425,7 +6435,7 @@
         <v>Building Operation Services</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="46">
         <v>25</v>
       </c>
@@ -6505,10 +6515,10 @@
         <v>Key-ABNT-25</v>
       </c>
       <c r="X25" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y25" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z25" s="50" t="s">
         <v>769</v>
@@ -6518,7 +6528,7 @@
         <v>Support Services</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="46">
         <v>26</v>
       </c>
@@ -6598,10 +6608,10 @@
         <v>Key-ABNT-26</v>
       </c>
       <c r="X26" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y26" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z26" s="50" t="s">
         <v>770</v>
@@ -6611,7 +6621,7 @@
         <v>Government Services</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="46">
         <v>27</v>
       </c>
@@ -6691,10 +6701,10 @@
         <v>Key-ABNT-27</v>
       </c>
       <c r="X27" s="35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="Y27" s="35" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z27" s="50" t="s">
         <v>771</v>
@@ -6706,20 +6716,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="18" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y2">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA27 A2:B27">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6727,13 +6745,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEF6990-269C-482F-AEAB-0F771E87FB19}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>657</v>
       </c>
@@ -6798,7 +6816,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -6880,13 +6898,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56C5A03-15CD-4694-84A2-E149E46D665B}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.83203125" customWidth="1"/>
+    <col min="2" max="3" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -6897,7 +6915,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -6922,27 +6940,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2864B2AC-DDFD-480C-BEC0-F2615FD9637A}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y305"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.796875" style="2" customWidth="1"/>
     <col min="4" max="5" width="8" style="2" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.33203125" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" customWidth="1"/>
-    <col min="10" max="10" width="3.6640625" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.296875" customWidth="1"/>
+    <col min="9" max="9" width="5.69921875" customWidth="1"/>
+    <col min="10" max="10" width="3.69921875" customWidth="1"/>
+    <col min="11" max="11" width="7.69921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.5" customWidth="1"/>
     <col min="13" max="13" width="27" customWidth="1"/>
-    <col min="14" max="14" width="6.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.296875" customWidth="1"/>
     <col min="15" max="15" width="32.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="3.83203125" customWidth="1"/>
+    <col min="17" max="17" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="3.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>319</v>
       </c>
@@ -7015,7 +7033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -7092,7 +7110,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -7169,7 +7187,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -7246,7 +7264,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -7323,7 +7341,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -7400,7 +7418,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -7477,7 +7495,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -7554,7 +7572,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -7631,7 +7649,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -7708,7 +7726,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -7785,7 +7803,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -7862,7 +7880,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -7939,7 +7957,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -8016,7 +8034,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -8093,7 +8111,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -8170,7 +8188,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -8247,7 +8265,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -8324,7 +8342,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -8401,7 +8419,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -8478,7 +8496,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -8555,7 +8573,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -8632,7 +8650,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -8709,7 +8727,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -8786,7 +8804,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -8863,7 +8881,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -8940,7 +8958,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -9017,7 +9035,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -9094,7 +9112,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -9171,7 +9189,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -9248,7 +9266,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -9325,7 +9343,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -9402,7 +9420,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -9479,7 +9497,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -9556,7 +9574,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -9633,7 +9651,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -9710,7 +9728,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -9787,7 +9805,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -9864,7 +9882,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -9941,7 +9959,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -10018,7 +10036,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -10095,7 +10113,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -10172,7 +10190,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -10249,7 +10267,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -10326,7 +10344,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -10403,7 +10421,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -10480,7 +10498,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -10557,7 +10575,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -10634,7 +10652,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -10711,7 +10729,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -10788,7 +10806,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -10865,7 +10883,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -10942,7 +10960,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -11019,7 +11037,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -11096,7 +11114,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -11173,7 +11191,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -11250,7 +11268,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -11327,7 +11345,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -11404,7 +11422,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -11481,7 +11499,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -11558,7 +11576,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -11635,7 +11653,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -11712,7 +11730,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -11789,7 +11807,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -11866,7 +11884,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -11943,7 +11961,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -12020,7 +12038,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -12097,7 +12115,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -12174,7 +12192,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -12251,7 +12269,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -12328,7 +12346,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -12405,7 +12423,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -12482,7 +12500,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -12559,7 +12577,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -12636,7 +12654,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -12713,7 +12731,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -12790,7 +12808,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -12867,7 +12885,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -12944,7 +12962,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -13021,7 +13039,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -13098,7 +13116,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -13175,7 +13193,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -13252,7 +13270,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -13329,7 +13347,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -13406,7 +13424,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -13483,7 +13501,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -13560,7 +13578,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -13637,7 +13655,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -13714,7 +13732,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -13791,7 +13809,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -13868,7 +13886,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -13945,7 +13963,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -14022,7 +14040,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -14099,7 +14117,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -14176,7 +14194,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -14253,7 +14271,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -14330,7 +14348,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -14407,7 +14425,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -14484,7 +14502,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -14561,7 +14579,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -14638,7 +14656,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -14715,7 +14733,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -14792,7 +14810,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -14869,7 +14887,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -14946,7 +14964,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -15023,7 +15041,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -15100,7 +15118,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -15177,7 +15195,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -15254,7 +15272,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -15331,7 +15349,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -15408,7 +15426,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -15485,7 +15503,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -15562,7 +15580,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -15639,7 +15657,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -15716,7 +15734,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -15793,7 +15811,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -15870,7 +15888,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -15947,7 +15965,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -16024,7 +16042,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -16101,7 +16119,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -16178,7 +16196,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -16255,7 +16273,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -16332,7 +16350,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -16409,7 +16427,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -16486,7 +16504,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -16563,7 +16581,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -16640,7 +16658,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -16717,7 +16735,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -16794,7 +16812,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -16871,7 +16889,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -16948,7 +16966,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -17025,7 +17043,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -17102,7 +17120,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -17179,7 +17197,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -17256,7 +17274,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -17333,7 +17351,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -17410,7 +17428,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -17487,7 +17505,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -17564,7 +17582,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -17641,7 +17659,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -17718,7 +17736,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -17795,7 +17813,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -17872,7 +17890,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -17949,7 +17967,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -18026,7 +18044,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -18103,7 +18121,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -18180,7 +18198,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -18257,7 +18275,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -18334,7 +18352,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -18411,7 +18429,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -18488,7 +18506,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -18565,7 +18583,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -18642,7 +18660,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -18719,7 +18737,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -18796,7 +18814,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -18873,7 +18891,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -18950,7 +18968,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="9">
         <v>157</v>
       </c>
@@ -19027,7 +19045,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="9">
         <v>158</v>
       </c>
@@ -19104,7 +19122,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="9">
         <v>159</v>
       </c>
@@ -19181,7 +19199,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="9">
         <v>160</v>
       </c>
@@ -19258,7 +19276,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="9">
         <v>161</v>
       </c>
@@ -19335,7 +19353,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="9">
         <v>162</v>
       </c>
@@ -19412,7 +19430,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="9">
         <v>163</v>
       </c>
@@ -19489,7 +19507,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="9">
         <v>164</v>
       </c>
@@ -19566,7 +19584,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="9">
         <v>165</v>
       </c>
@@ -19643,7 +19661,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="9">
         <v>166</v>
       </c>
@@ -19720,7 +19738,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="9">
         <v>167</v>
       </c>
@@ -19797,7 +19815,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>168</v>
       </c>
@@ -19874,7 +19892,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="9">
         <v>169</v>
       </c>
@@ -19951,7 +19969,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="9">
         <v>170</v>
       </c>
@@ -20028,7 +20046,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="9">
         <v>171</v>
       </c>
@@ -20105,7 +20123,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="9">
         <v>172</v>
       </c>
@@ -20182,7 +20200,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="9">
         <v>173</v>
       </c>
@@ -20259,7 +20277,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="9">
         <v>174</v>
       </c>
@@ -20336,7 +20354,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="9">
         <v>175</v>
       </c>
@@ -20413,7 +20431,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="9">
         <v>176</v>
       </c>
@@ -20490,7 +20508,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="9">
         <v>177</v>
       </c>
@@ -20567,7 +20585,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="9">
         <v>178</v>
       </c>
@@ -20644,7 +20662,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="9">
         <v>179</v>
       </c>
@@ -20721,7 +20739,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="9">
         <v>180</v>
       </c>
@@ -20798,7 +20816,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="9">
         <v>181</v>
       </c>
@@ -20875,7 +20893,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="9">
         <v>182</v>
       </c>
@@ -20952,7 +20970,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="9">
         <v>183</v>
       </c>
@@ -21029,7 +21047,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="9">
         <v>184</v>
       </c>
@@ -21106,7 +21124,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="9">
         <v>185</v>
       </c>
@@ -21183,7 +21201,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="9">
         <v>186</v>
       </c>
@@ -21260,7 +21278,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="9">
         <v>187</v>
       </c>
@@ -21337,7 +21355,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="9">
         <v>188</v>
       </c>
@@ -21414,7 +21432,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="9">
         <v>189</v>
       </c>
@@ -21491,7 +21509,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="9">
         <v>190</v>
       </c>
@@ -21568,7 +21586,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="9">
         <v>191</v>
       </c>
@@ -21645,7 +21663,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="9">
         <v>192</v>
       </c>
@@ -21722,7 +21740,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="9">
         <v>193</v>
       </c>
@@ -21799,7 +21817,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="9">
         <v>194</v>
       </c>
@@ -21876,7 +21894,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="9">
         <v>195</v>
       </c>
@@ -21953,7 +21971,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="9">
         <v>196</v>
       </c>
@@ -22030,7 +22048,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="9">
         <v>197</v>
       </c>
@@ -22107,7 +22125,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="9">
         <v>198</v>
       </c>
@@ -22184,7 +22202,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="9">
         <v>199</v>
       </c>
@@ -22261,7 +22279,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="9">
         <v>200</v>
       </c>
@@ -22338,7 +22356,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="9">
         <v>201</v>
       </c>
@@ -22415,7 +22433,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="9">
         <v>202</v>
       </c>
@@ -22492,7 +22510,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="9">
         <v>203</v>
       </c>
@@ -22569,7 +22587,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="9">
         <v>204</v>
       </c>
@@ -22646,7 +22664,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="9">
         <v>205</v>
       </c>
@@ -22723,7 +22741,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="9">
         <v>206</v>
       </c>
@@ -22800,7 +22818,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="9">
         <v>207</v>
       </c>
@@ -22877,7 +22895,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="9">
         <v>208</v>
       </c>
@@ -22954,7 +22972,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="9">
         <v>209</v>
       </c>
@@ -23031,7 +23049,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="9">
         <v>210</v>
       </c>
@@ -23108,7 +23126,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="9">
         <v>211</v>
       </c>
@@ -23185,7 +23203,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="9">
         <v>212</v>
       </c>
@@ -23262,7 +23280,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="9">
         <v>213</v>
       </c>
@@ -23339,7 +23357,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="9">
         <v>214</v>
       </c>
@@ -23416,7 +23434,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="9">
         <v>215</v>
       </c>
@@ -23493,7 +23511,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="9">
         <v>216</v>
       </c>
@@ -23570,7 +23588,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="9">
         <v>217</v>
       </c>
@@ -23647,7 +23665,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="9">
         <v>218</v>
       </c>
@@ -23724,7 +23742,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="9">
         <v>219</v>
       </c>
@@ -23801,7 +23819,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="9">
         <v>220</v>
       </c>
@@ -23878,7 +23896,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="9">
         <v>221</v>
       </c>
@@ -23955,7 +23973,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="9">
         <v>222</v>
       </c>
@@ -24032,7 +24050,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="9">
         <v>223</v>
       </c>
@@ -24109,7 +24127,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="9">
         <v>224</v>
       </c>
@@ -24186,7 +24204,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="9">
         <v>225</v>
       </c>
@@ -24263,7 +24281,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="9">
         <v>226</v>
       </c>
@@ -24340,7 +24358,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="9">
         <v>227</v>
       </c>
@@ -24417,7 +24435,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="9">
         <v>228</v>
       </c>
@@ -24494,7 +24512,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="9">
         <v>229</v>
       </c>
@@ -24571,7 +24589,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="9">
         <v>230</v>
       </c>
@@ -24648,7 +24666,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="9">
         <v>231</v>
       </c>
@@ -24725,7 +24743,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="9">
         <v>232</v>
       </c>
@@ -24802,7 +24820,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="9">
         <v>233</v>
       </c>
@@ -24879,7 +24897,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="9">
         <v>234</v>
       </c>
@@ -24956,7 +24974,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="9">
         <v>235</v>
       </c>
@@ -25033,7 +25051,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="9">
         <v>236</v>
       </c>
@@ -25110,7 +25128,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="9">
         <v>237</v>
       </c>
@@ -25187,7 +25205,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="9">
         <v>238</v>
       </c>
@@ -25264,7 +25282,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="9">
         <v>239</v>
       </c>
@@ -25341,7 +25359,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="9">
         <v>240</v>
       </c>
@@ -25418,7 +25436,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="9">
         <v>241</v>
       </c>
@@ -25495,7 +25513,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="9">
         <v>242</v>
       </c>
@@ -25572,7 +25590,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="9">
         <v>243</v>
       </c>
@@ -25649,7 +25667,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="9">
         <v>244</v>
       </c>
@@ -25726,7 +25744,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="9">
         <v>245</v>
       </c>
@@ -25803,7 +25821,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="9">
         <v>246</v>
       </c>
@@ -25880,7 +25898,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="9">
         <v>247</v>
       </c>
@@ -25957,7 +25975,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="9">
         <v>248</v>
       </c>
@@ -26034,7 +26052,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="9">
         <v>249</v>
       </c>
@@ -26111,7 +26129,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="9">
         <v>250</v>
       </c>
@@ -26188,7 +26206,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="9">
         <v>251</v>
       </c>
@@ -26265,7 +26283,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="9">
         <v>252</v>
       </c>
@@ -26342,7 +26360,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="9">
         <v>253</v>
       </c>
@@ -26419,7 +26437,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="9">
         <v>254</v>
       </c>
@@ -26496,7 +26514,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="9">
         <v>255</v>
       </c>
@@ -26573,7 +26591,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="9">
         <v>256</v>
       </c>
@@ -26650,7 +26668,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="9">
         <v>257</v>
       </c>
@@ -26727,7 +26745,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="9">
         <v>258</v>
       </c>
@@ -26804,7 +26822,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="9">
         <v>259</v>
       </c>
@@ -26881,7 +26899,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="9">
         <v>260</v>
       </c>
@@ -26958,7 +26976,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="9">
         <v>261</v>
       </c>
@@ -27035,7 +27053,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="9">
         <v>262</v>
       </c>
@@ -27112,7 +27130,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="9">
         <v>263</v>
       </c>
@@ -27189,7 +27207,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="9">
         <v>264</v>
       </c>
@@ -27266,7 +27284,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="9">
         <v>265</v>
       </c>
@@ -27343,7 +27361,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="9">
         <v>266</v>
       </c>
@@ -27420,7 +27438,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="9">
         <v>267</v>
       </c>
@@ -27497,7 +27515,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="9">
         <v>268</v>
       </c>
@@ -27574,7 +27592,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="9">
         <v>269</v>
       </c>
@@ -27651,7 +27669,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="9">
         <v>270</v>
       </c>
@@ -27728,7 +27746,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="9">
         <v>271</v>
       </c>
@@ -27805,7 +27823,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="9">
         <v>272</v>
       </c>
@@ -27882,7 +27900,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="9">
         <v>273</v>
       </c>
@@ -27959,7 +27977,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="9">
         <v>274</v>
       </c>
@@ -28036,7 +28054,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="9">
         <v>275</v>
       </c>
@@ -28113,7 +28131,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="9">
         <v>276</v>
       </c>
@@ -28190,7 +28208,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="9">
         <v>277</v>
       </c>
@@ -28267,7 +28285,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="9">
         <v>278</v>
       </c>
@@ -28344,7 +28362,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="9">
         <v>279</v>
       </c>
@@ -28421,7 +28439,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="9">
         <v>280</v>
       </c>
@@ -28498,7 +28516,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="9">
         <v>281</v>
       </c>
@@ -28575,7 +28593,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="9">
         <v>282</v>
       </c>
@@ -28652,7 +28670,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="9">
         <v>283</v>
       </c>
@@ -28729,7 +28747,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="9">
         <v>284</v>
       </c>
@@ -28806,7 +28824,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="9">
         <v>285</v>
       </c>
@@ -28883,7 +28901,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="9">
         <v>286</v>
       </c>
@@ -28960,7 +28978,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="9">
         <v>287</v>
       </c>
@@ -29037,7 +29055,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="9">
         <v>288</v>
       </c>
@@ -29114,7 +29132,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="9">
         <v>289</v>
       </c>
@@ -29191,7 +29209,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="9">
         <v>290</v>
       </c>
@@ -29268,7 +29286,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="9">
         <v>291</v>
       </c>
@@ -29345,7 +29363,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="9">
         <v>292</v>
       </c>
@@ -29422,7 +29440,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="9">
         <v>293</v>
       </c>
@@ -29499,7 +29517,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="9">
         <v>294</v>
       </c>
@@ -29576,7 +29594,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="9">
         <v>295</v>
       </c>
@@ -29653,7 +29671,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="9">
         <v>296</v>
       </c>
@@ -29730,7 +29748,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="9">
         <v>297</v>
       </c>
@@ -29807,7 +29825,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="9">
         <v>298</v>
       </c>
@@ -29884,7 +29902,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="9">
         <v>299</v>
       </c>
@@ -29961,7 +29979,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="9">
         <v>300</v>
       </c>
@@ -30038,7 +30056,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="9">
         <v>301</v>
       </c>
@@ -30115,7 +30133,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="9">
         <v>302</v>
       </c>
@@ -30192,7 +30210,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="9">
         <v>303</v>
       </c>
@@ -30269,7 +30287,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="9">
         <v>304</v>
       </c>
@@ -30346,7 +30364,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="9">
         <v>305</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1S.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814B19DC-B791-49AF-B906-DDD54CEF0F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183AA952-638C-4580-A5B0-64E1218080B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7945" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8025" uniqueCount="896">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2695,6 +2695,90 @@
   </si>
   <si>
     <t>[ IfcSpace : IfcRelSpaceBoundary : IfcSpaceType : IfcSpaceTypeEnum ]</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Atributo Ifc</t>
+  </si>
+  <si>
+    <t>Transactional services</t>
+  </si>
+  <si>
+    <t>Administrative services</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Conceptualization Services</t>
+  </si>
+  <si>
+    <t>Information services</t>
+  </si>
+  <si>
+    <t>Organization Services</t>
+  </si>
+  <si>
+    <t>Project Development Services</t>
+  </si>
+  <si>
+    <t>Document Services</t>
+  </si>
+  <si>
+    <t>Implementation Services</t>
+  </si>
+  <si>
+    <t>Building Operation Services</t>
+  </si>
+  <si>
+    <t>Support Services</t>
+  </si>
+  <si>
+    <t>Government Services</t>
+  </si>
+  <si>
+    <t>Additional services</t>
+  </si>
+  <si>
+    <t>Servicios transaccionales</t>
+  </si>
+  <si>
+    <t>Servicios administrativos</t>
+  </si>
+  <si>
+    <t>Servicios de comunicación</t>
+  </si>
+  <si>
+    <t>Servicios de Conceptualización</t>
+  </si>
+  <si>
+    <t>Servicios de información</t>
+  </si>
+  <si>
+    <t>Servicios de organización</t>
+  </si>
+  <si>
+    <t>Servicios de Desarrollo de Proyectos</t>
+  </si>
+  <si>
+    <t>Servicios de Documentos</t>
+  </si>
+  <si>
+    <t>Servicios de Implementación</t>
+  </si>
+  <si>
+    <t>Servicios de Operación de Edificios</t>
+  </si>
+  <si>
+    <t>Servicios de apoyo</t>
+  </si>
+  <si>
+    <t>Servicios gubernamentales</t>
+  </si>
+  <si>
+    <t>Servicios adicionales</t>
   </si>
 </sst>
 </file>
@@ -3238,7 +3322,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{75D7255F-4B16-4C61-A12B-6DBA4ACA1970}"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="22">
     <dxf>
       <font>
         <b val="0"/>
@@ -3351,6 +3435,14 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -3755,14 +3847,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CFA2BD-3953-447B-BF8D-35BA528839AD}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -3773,7 +3865,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>307</v>
       </c>
@@ -3784,7 +3876,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>308</v>
       </c>
@@ -3795,7 +3887,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -3806,7 +3898,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -3818,7 +3910,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -3830,7 +3922,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -3841,7 +3933,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="36" t="s">
         <v>9</v>
       </c>
@@ -3852,7 +3944,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>309</v>
       </c>
@@ -3863,7 +3955,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>311</v>
       </c>
@@ -3874,7 +3966,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>312</v>
       </c>
@@ -3885,7 +3977,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -3896,7 +3988,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>313</v>
       </c>
@@ -3907,7 +3999,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>314</v>
       </c>
@@ -3918,7 +4010,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>315</v>
       </c>
@@ -3929,7 +4021,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>316</v>
       </c>
@@ -3940,7 +4032,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -3951,19 +4043,19 @@
         <v>689</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>317</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46249.322863657406</v>
+        <v>46253.603557175928</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>698</v>
       </c>
@@ -3974,7 +4066,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="36" t="s">
         <v>692</v>
       </c>
@@ -3986,7 +4078,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="36" t="s">
         <v>699</v>
       </c>
@@ -3998,7 +4090,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>306</v>
       </c>
@@ -4009,7 +4101,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>318</v>
       </c>
@@ -4020,7 +4112,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>324</v>
       </c>
@@ -4031,7 +4123,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>326</v>
       </c>
@@ -4042,7 +4134,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="36" t="s">
         <v>685</v>
       </c>
@@ -4053,7 +4145,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="36" t="s">
         <v>827</v>
       </c>
@@ -4064,7 +4156,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="36" t="s">
         <v>829</v>
       </c>
@@ -4075,7 +4167,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="36" t="s">
         <v>831</v>
       </c>
@@ -4086,7 +4178,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="36" t="s">
         <v>833</v>
       </c>
@@ -4097,7 +4189,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="36" t="s">
         <v>835</v>
       </c>
@@ -4108,7 +4200,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="36" t="s">
         <v>837</v>
       </c>
@@ -4119,7 +4211,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="36" t="s">
         <v>839</v>
       </c>
@@ -4130,7 +4222,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="36" t="s">
         <v>841</v>
       </c>
@@ -4141,7 +4233,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="36" t="s">
         <v>843</v>
       </c>
@@ -4152,7 +4244,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="36" t="s">
         <v>845</v>
       </c>
@@ -4163,7 +4255,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="36" t="s">
         <v>847</v>
       </c>
@@ -4174,7 +4266,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>849</v>
       </c>
@@ -4185,7 +4277,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="62" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="62" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="36" t="s">
         <v>851</v>
       </c>
@@ -4211,35 +4303,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6EEAB6-D26C-4450-83AD-F740CF51FA1E}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA27"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC27"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.09765625" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.8984375" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.296875" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3984375" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.3984375" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="62.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="65" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.796875" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.09765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.8984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="45.59765625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="35.69921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.296875" customWidth="1"/>
-    <col min="27" max="27" width="57.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.5" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="45.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>637</v>
       </c>
@@ -4291,38 +4385,44 @@
       <c r="Q1" s="17" t="s">
         <v>653</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="34" t="s">
+        <v>684</v>
+      </c>
+      <c r="S1" s="17" t="s">
         <v>678</v>
       </c>
-      <c r="S1" s="17" t="s">
+      <c r="T1" s="17" t="s">
         <v>634</v>
       </c>
-      <c r="T1" s="17" t="s">
+      <c r="U1" s="17" t="s">
         <v>654</v>
       </c>
-      <c r="U1" s="17" t="s">
+      <c r="V1" s="17" t="s">
         <v>636</v>
       </c>
-      <c r="V1" s="17" t="s">
+      <c r="W1" s="17" t="s">
         <v>635</v>
       </c>
-      <c r="W1" s="55" t="s">
+      <c r="X1" s="55" t="s">
         <v>655</v>
       </c>
-      <c r="X1" s="17" t="s">
+      <c r="Y1" s="17" t="s">
         <v>682</v>
       </c>
-      <c r="Y1" s="17" t="s">
+      <c r="Z1" s="17" t="s">
+        <v>868</v>
+      </c>
+      <c r="AA1" s="17" t="s">
         <v>683</v>
       </c>
-      <c r="Z1" s="17" t="s">
+      <c r="AB1" s="17" t="s">
+        <v>869</v>
+      </c>
+      <c r="AC1" s="17" t="s">
         <v>656</v>
       </c>
-      <c r="AA1" s="34" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="46">
         <v>2</v>
       </c>
@@ -4378,42 +4478,48 @@
       <c r="Q2" s="49" t="s">
         <v>789</v>
       </c>
-      <c r="R2" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S2" s="50" t="str">
-        <f t="shared" ref="S2:U14" si="2">SUBSTITUTE(C2, "_", " ")</f>
+      <c r="R2" s="51" t="s">
+        <v>790</v>
+      </c>
+      <c r="S2" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T2" s="50" t="str">
+        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T2" s="50" t="str">
+      <c r="U2" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U2" s="49" t="str">
+      <c r="V2" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V2" s="35" t="s">
+      <c r="W2" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W2" s="54" t="str">
-        <f t="shared" ref="W2:W14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
+      <c r="X2" s="54" t="str">
+        <f t="shared" ref="X2:X14" si="3">CONCATENATE("Key-ABNT-",A2)</f>
         <v>Key-ABNT-2</v>
       </c>
-      <c r="X2" s="35" t="s">
+      <c r="Y2" s="35" t="s">
         <v>863</v>
       </c>
-      <c r="Y2" s="35" t="s">
+      <c r="Z2" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA2" s="35" t="s">
         <v>864</v>
       </c>
-      <c r="Z2" s="35" t="s">
+      <c r="AB2" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC2" s="35" t="s">
         <v>706</v>
       </c>
-      <c r="AA2" s="51" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="46">
         <v>3</v>
       </c>
@@ -4469,42 +4575,48 @@
       <c r="Q3" s="49" t="s">
         <v>792</v>
       </c>
-      <c r="R3" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S3" s="50" t="str">
+      <c r="R3" s="51" t="s">
+        <v>793</v>
+      </c>
+      <c r="S3" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T3" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T3" s="50" t="str">
+      <c r="U3" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U3" s="49" t="str">
+      <c r="V3" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V3" s="35" t="s">
+      <c r="W3" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W3" s="54" t="str">
+      <c r="X3" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-3</v>
       </c>
-      <c r="X3" s="35" t="s">
+      <c r="Y3" s="35" t="s">
         <v>865</v>
       </c>
-      <c r="Y3" s="35" t="s">
+      <c r="Z3" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA3" s="35" t="s">
         <v>866</v>
       </c>
-      <c r="Z3" s="35" t="s">
+      <c r="AB3" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC3" s="35" t="s">
         <v>707</v>
       </c>
-      <c r="AA3" s="51" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="46">
         <v>4</v>
       </c>
@@ -4560,42 +4672,48 @@
       <c r="Q4" s="49" t="s">
         <v>795</v>
       </c>
-      <c r="R4" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S4" s="50" t="str">
+      <c r="R4" s="51" t="s">
+        <v>796</v>
+      </c>
+      <c r="S4" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T4" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T4" s="50" t="str">
+      <c r="U4" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U4" s="49" t="str">
+      <c r="V4" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V4" s="35" t="s">
+      <c r="W4" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W4" s="54" t="str">
+      <c r="X4" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-4</v>
       </c>
-      <c r="X4" s="35" t="s">
+      <c r="Y4" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y4" s="35" t="s">
+      <c r="Z4" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA4" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z4" s="35" t="s">
+      <c r="AB4" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC4" s="35" t="s">
         <v>708</v>
       </c>
-      <c r="AA4" s="51" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46">
         <v>5</v>
       </c>
@@ -4651,42 +4769,48 @@
       <c r="Q5" s="49" t="s">
         <v>798</v>
       </c>
-      <c r="R5" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S5" s="50" t="str">
+      <c r="R5" s="51" t="s">
+        <v>799</v>
+      </c>
+      <c r="S5" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T5" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T5" s="50" t="str">
+      <c r="U5" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U5" s="49" t="str">
+      <c r="V5" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V5" s="35" t="s">
+      <c r="W5" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W5" s="54" t="str">
+      <c r="X5" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-5</v>
       </c>
-      <c r="X5" s="35" t="s">
+      <c r="Y5" s="35" t="s">
         <v>858</v>
       </c>
-      <c r="Y5" s="35" t="s">
+      <c r="Z5" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA5" s="35" t="s">
         <v>859</v>
       </c>
-      <c r="Z5" s="35" t="s">
+      <c r="AB5" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC5" s="35" t="s">
         <v>709</v>
       </c>
-      <c r="AA5" s="51" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="46">
         <v>6</v>
       </c>
@@ -4742,42 +4866,48 @@
       <c r="Q6" s="49" t="s">
         <v>801</v>
       </c>
-      <c r="R6" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S6" s="50" t="str">
+      <c r="R6" s="51" t="s">
+        <v>802</v>
+      </c>
+      <c r="S6" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T6" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T6" s="50" t="str">
+      <c r="U6" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U6" s="49" t="str">
+      <c r="V6" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V6" s="35" t="s">
+      <c r="W6" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W6" s="54" t="str">
+      <c r="X6" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-6</v>
       </c>
-      <c r="X6" s="35" t="s">
+      <c r="Y6" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y6" s="35" t="s">
+      <c r="Z6" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA6" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z6" s="35" t="s">
+      <c r="AB6" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC6" s="35" t="s">
         <v>624</v>
       </c>
-      <c r="AA6" s="51" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="46">
         <v>7</v>
       </c>
@@ -4833,42 +4963,48 @@
       <c r="Q7" s="49" t="s">
         <v>804</v>
       </c>
-      <c r="R7" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S7" s="50" t="str">
+      <c r="R7" s="51" t="s">
+        <v>805</v>
+      </c>
+      <c r="S7" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T7" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T7" s="50" t="str">
+      <c r="U7" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U7" s="49" t="str">
+      <c r="V7" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V7" s="35" t="s">
+      <c r="W7" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W7" s="54" t="str">
+      <c r="X7" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-7</v>
       </c>
-      <c r="X7" s="35" t="s">
-        <v>856</v>
-      </c>
       <c r="Y7" s="35" t="s">
         <v>856</v>
       </c>
       <c r="Z7" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA7" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AB7" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC7" s="35" t="s">
         <v>710</v>
       </c>
-      <c r="AA7" s="51" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="46">
         <v>8</v>
       </c>
@@ -4924,42 +5060,48 @@
       <c r="Q8" s="49" t="s">
         <v>807</v>
       </c>
-      <c r="R8" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S8" s="50" t="str">
+      <c r="R8" s="51" t="s">
+        <v>808</v>
+      </c>
+      <c r="S8" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T8" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T8" s="50" t="str">
+      <c r="U8" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U8" s="49" t="str">
+      <c r="V8" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V8" s="35" t="s">
+      <c r="W8" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W8" s="54" t="str">
+      <c r="X8" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-8</v>
       </c>
-      <c r="X8" s="35" t="s">
-        <v>856</v>
-      </c>
       <c r="Y8" s="35" t="s">
         <v>856</v>
       </c>
       <c r="Z8" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA8" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AB8" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC8" s="35" t="s">
         <v>711</v>
       </c>
-      <c r="AA8" s="51" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="46">
         <v>9</v>
       </c>
@@ -5015,42 +5157,48 @@
       <c r="Q9" s="49" t="s">
         <v>810</v>
       </c>
-      <c r="R9" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S9" s="50" t="str">
+      <c r="R9" s="51" t="s">
+        <v>811</v>
+      </c>
+      <c r="S9" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T9" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T9" s="50" t="str">
+      <c r="U9" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U9" s="49" t="str">
+      <c r="V9" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V9" s="35" t="s">
+      <c r="W9" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W9" s="54" t="str">
+      <c r="X9" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-9</v>
       </c>
-      <c r="X9" s="35" t="s">
-        <v>856</v>
-      </c>
       <c r="Y9" s="35" t="s">
         <v>856</v>
       </c>
       <c r="Z9" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA9" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AB9" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC9" s="35" t="s">
         <v>712</v>
       </c>
-      <c r="AA9" s="51" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="46">
         <v>10</v>
       </c>
@@ -5106,42 +5254,48 @@
       <c r="Q10" s="49" t="s">
         <v>813</v>
       </c>
-      <c r="R10" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S10" s="50" t="str">
+      <c r="R10" s="51" t="s">
+        <v>814</v>
+      </c>
+      <c r="S10" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T10" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T10" s="50" t="str">
+      <c r="U10" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U10" s="49" t="str">
+      <c r="V10" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V10" s="35" t="s">
+      <c r="W10" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W10" s="54" t="str">
+      <c r="X10" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-10</v>
       </c>
-      <c r="X10" s="35" t="s">
-        <v>856</v>
-      </c>
       <c r="Y10" s="35" t="s">
         <v>856</v>
       </c>
       <c r="Z10" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA10" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AB10" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC10" s="35" t="s">
         <v>713</v>
       </c>
-      <c r="AA10" s="51" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="46">
         <v>11</v>
       </c>
@@ -5197,42 +5351,48 @@
       <c r="Q11" s="49" t="s">
         <v>816</v>
       </c>
-      <c r="R11" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S11" s="50" t="str">
+      <c r="R11" s="51" t="s">
+        <v>817</v>
+      </c>
+      <c r="S11" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T11" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T11" s="50" t="str">
+      <c r="U11" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U11" s="49" t="str">
+      <c r="V11" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V11" s="35" t="s">
+      <c r="W11" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W11" s="54" t="str">
+      <c r="X11" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-11</v>
       </c>
-      <c r="X11" s="35" t="s">
-        <v>856</v>
-      </c>
       <c r="Y11" s="35" t="s">
         <v>856</v>
       </c>
       <c r="Z11" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA11" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AB11" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC11" s="35" t="s">
         <v>714</v>
       </c>
-      <c r="AA11" s="51" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="46">
         <v>12</v>
       </c>
@@ -5288,42 +5448,48 @@
       <c r="Q12" s="49" t="s">
         <v>819</v>
       </c>
-      <c r="R12" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S12" s="50" t="str">
+      <c r="R12" s="51" t="s">
+        <v>820</v>
+      </c>
+      <c r="S12" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T12" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T12" s="50" t="str">
+      <c r="U12" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U12" s="49" t="str">
+      <c r="V12" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V12" s="35" t="s">
+      <c r="W12" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W12" s="54" t="str">
+      <c r="X12" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-12</v>
       </c>
-      <c r="X12" s="35" t="s">
+      <c r="Y12" s="35" t="s">
         <v>860</v>
       </c>
-      <c r="Y12" s="35" t="s">
+      <c r="Z12" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA12" s="35" t="s">
         <v>867</v>
       </c>
-      <c r="Z12" s="35" t="s">
+      <c r="AB12" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC12" s="35" t="s">
         <v>715</v>
       </c>
-      <c r="AA12" s="51" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="46">
         <v>13</v>
       </c>
@@ -5379,42 +5545,48 @@
       <c r="Q13" s="49" t="s">
         <v>822</v>
       </c>
-      <c r="R13" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S13" s="50" t="str">
+      <c r="R13" s="51" t="s">
+        <v>823</v>
+      </c>
+      <c r="S13" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T13" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T13" s="50" t="str">
+      <c r="U13" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U13" s="49" t="str">
+      <c r="V13" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V13" s="35" t="s">
+      <c r="W13" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W13" s="54" t="str">
+      <c r="X13" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-13</v>
       </c>
-      <c r="X13" s="35" t="s">
+      <c r="Y13" s="35" t="s">
         <v>860</v>
       </c>
-      <c r="Y13" s="35" t="s">
+      <c r="Z13" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA13" s="35" t="s">
         <v>867</v>
       </c>
-      <c r="Z13" s="35" t="s">
+      <c r="AB13" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC13" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="AA13" s="51" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="46">
         <v>14</v>
       </c>
@@ -5470,42 +5642,48 @@
       <c r="Q14" s="49" t="s">
         <v>825</v>
       </c>
-      <c r="R14" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S14" s="50" t="str">
+      <c r="R14" s="51" t="s">
+        <v>826</v>
+      </c>
+      <c r="S14" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T14" s="50" t="str">
         <f t="shared" si="2"/>
         <v>Normativos</v>
       </c>
-      <c r="T14" s="50" t="str">
+      <c r="U14" s="50" t="str">
         <f t="shared" si="2"/>
         <v>ABNT</v>
       </c>
-      <c r="U14" s="49" t="str">
+      <c r="V14" s="49" t="str">
         <f t="shared" si="2"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="V14" s="35" t="s">
+      <c r="W14" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W14" s="54" t="str">
+      <c r="X14" s="54" t="str">
         <f t="shared" si="3"/>
         <v>Key-ABNT-14</v>
       </c>
-      <c r="X14" s="63" t="s">
+      <c r="Y14" s="63" t="s">
         <v>861</v>
       </c>
-      <c r="Y14" s="64" t="s">
+      <c r="Z14" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA14" s="64" t="s">
         <v>862</v>
       </c>
-      <c r="Z14" s="35" t="s">
+      <c r="AB14" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC14" s="35" t="s">
         <v>717</v>
       </c>
-      <c r="AA14" s="51" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="46">
         <v>15</v>
       </c>
@@ -5558,47 +5736,51 @@
       <c r="P15" s="35" t="s">
         <v>748</v>
       </c>
-      <c r="Q15" s="35" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","es")</f>
-        <v>Servicios transaccionales</v>
+      <c r="Q15" s="35" t="s">
+        <v>883</v>
       </c>
       <c r="R15" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S15" s="50" t="str">
-        <f t="shared" ref="S15:U17" si="6">SUBSTITUTE(C15, "_", " ")</f>
+        <v>870</v>
+      </c>
+      <c r="S15" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T15" s="50" t="str">
+        <f t="shared" ref="T15:V17" si="6">SUBSTITUTE(C15, "_", " ")</f>
         <v>Normativos</v>
       </c>
-      <c r="T15" s="50" t="str">
+      <c r="U15" s="50" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U15" s="49" t="str">
+      <c r="V15" s="49" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V15" s="35" t="s">
+      <c r="W15" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W15" s="54" t="str">
-        <f t="shared" ref="W15:W27" si="7">CONCATENATE("Key-ABNT-",A15)</f>
+      <c r="X15" s="54" t="str">
+        <f t="shared" ref="X15:X27" si="7">CONCATENATE("Key-ABNT-",A15)</f>
         <v>Key-ABNT-15</v>
       </c>
-      <c r="X15" s="35" t="s">
+      <c r="Y15" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y15" s="35" t="s">
+      <c r="Z15" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA15" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z15" s="50" t="s">
+      <c r="AB15" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC15" s="50" t="s">
         <v>746</v>
       </c>
-      <c r="AA15" s="35" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","en")</f>
-        <v>Transactional services</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="46">
         <v>16</v>
       </c>
@@ -5651,47 +5833,51 @@
       <c r="P16" s="49" t="s">
         <v>749</v>
       </c>
-      <c r="Q16" s="35" t="str">
-        <f t="shared" ref="Q16:Q27" si="8">_xlfn.TRANSLATE(P16,"pt","es")</f>
-        <v>Servicios administrativos</v>
+      <c r="Q16" s="35" t="s">
+        <v>884</v>
       </c>
       <c r="R16" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S16" s="50" t="str">
+        <v>871</v>
+      </c>
+      <c r="S16" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T16" s="50" t="str">
         <f t="shared" si="6"/>
         <v>Normativos</v>
       </c>
-      <c r="T16" s="50" t="str">
+      <c r="U16" s="50" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U16" s="49" t="str">
+      <c r="V16" s="49" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V16" s="35" t="s">
+      <c r="W16" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W16" s="54" t="str">
+      <c r="X16" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-16</v>
       </c>
-      <c r="X16" s="35" t="s">
+      <c r="Y16" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y16" s="35" t="s">
+      <c r="Z16" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA16" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z16" s="50" t="s">
+      <c r="AB16" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC16" s="50" t="s">
         <v>747</v>
       </c>
-      <c r="AA16" s="35" t="str">
-        <f t="shared" ref="AA16:AA27" si="9">_xlfn.TRANSLATE(P16,"pt","en")</f>
-        <v>Administrative services</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="46">
         <v>17</v>
       </c>
@@ -5744,47 +5930,51 @@
       <c r="P17" s="49" t="s">
         <v>750</v>
       </c>
-      <c r="Q17" s="35" t="str">
-        <f t="shared" si="8"/>
-        <v>Servicios de comunicación</v>
+      <c r="Q17" s="35" t="s">
+        <v>885</v>
       </c>
       <c r="R17" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S17" s="50" t="str">
+        <v>872</v>
+      </c>
+      <c r="S17" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T17" s="50" t="str">
         <f t="shared" si="6"/>
         <v>Normativos</v>
       </c>
-      <c r="T17" s="50" t="str">
+      <c r="U17" s="50" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U17" s="49" t="str">
+      <c r="V17" s="49" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V17" s="35" t="s">
+      <c r="W17" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W17" s="54" t="str">
+      <c r="X17" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-17</v>
       </c>
-      <c r="X17" s="35" t="s">
+      <c r="Y17" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y17" s="35" t="s">
+      <c r="Z17" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA17" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z17" s="50" t="s">
+      <c r="AB17" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC17" s="50" t="s">
         <v>761</v>
       </c>
-      <c r="AA17" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Communication Services</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="46">
         <v>18</v>
       </c>
@@ -5837,47 +6027,51 @@
       <c r="P18" s="49" t="s">
         <v>751</v>
       </c>
-      <c r="Q18" s="35" t="str">
+      <c r="Q18" s="35" t="s">
+        <v>886</v>
+      </c>
+      <c r="R18" s="35" t="s">
+        <v>873</v>
+      </c>
+      <c r="S18" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T18" s="50" t="str">
+        <f t="shared" ref="T18:V27" si="8">SUBSTITUTE(C18, "_", " ")</f>
+        <v>Normativos</v>
+      </c>
+      <c r="U18" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Servicios de Conceptualización</v>
-      </c>
-      <c r="R18" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S18" s="50" t="str">
-        <f t="shared" ref="S18:U27" si="10">SUBSTITUTE(C18, "_", " ")</f>
-        <v>Normativos</v>
-      </c>
-      <c r="T18" s="50" t="str">
-        <f t="shared" si="10"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U18" s="49" t="str">
-        <f t="shared" si="10"/>
+      <c r="V18" s="49" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V18" s="35" t="s">
+      <c r="W18" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W18" s="54" t="str">
+      <c r="X18" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-18</v>
       </c>
-      <c r="X18" s="35" t="s">
+      <c r="Y18" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y18" s="35" t="s">
+      <c r="Z18" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA18" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z18" s="50" t="s">
+      <c r="AB18" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC18" s="50" t="s">
         <v>762</v>
       </c>
-      <c r="AA18" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Conceptualization Services</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="46">
         <v>19</v>
       </c>
@@ -5930,47 +6124,51 @@
       <c r="P19" s="49" t="s">
         <v>752</v>
       </c>
-      <c r="Q19" s="35" t="str">
+      <c r="Q19" s="35" t="s">
+        <v>887</v>
+      </c>
+      <c r="R19" s="35" t="s">
+        <v>874</v>
+      </c>
+      <c r="S19" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T19" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Servicios de información</v>
-      </c>
-      <c r="R19" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S19" s="50" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T19" s="50" t="str">
-        <f t="shared" si="10"/>
+      <c r="U19" s="50" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U19" s="49" t="str">
-        <f t="shared" si="10"/>
+      <c r="V19" s="49" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V19" s="35" t="s">
+      <c r="W19" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W19" s="54" t="str">
+      <c r="X19" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-19</v>
       </c>
-      <c r="X19" s="35" t="s">
+      <c r="Y19" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y19" s="35" t="s">
+      <c r="Z19" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA19" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z19" s="50" t="s">
+      <c r="AB19" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC19" s="50" t="s">
         <v>765</v>
       </c>
-      <c r="AA19" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Information services</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="46">
         <v>20</v>
       </c>
@@ -6023,47 +6221,51 @@
       <c r="P20" s="49" t="s">
         <v>753</v>
       </c>
-      <c r="Q20" s="35" t="str">
+      <c r="Q20" s="35" t="s">
+        <v>888</v>
+      </c>
+      <c r="R20" s="35" t="s">
+        <v>875</v>
+      </c>
+      <c r="S20" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T20" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Servicios de organización</v>
-      </c>
-      <c r="R20" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S20" s="50" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T20" s="50" t="str">
-        <f t="shared" si="10"/>
+      <c r="U20" s="50" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U20" s="49" t="str">
-        <f t="shared" si="10"/>
+      <c r="V20" s="49" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V20" s="35" t="s">
+      <c r="W20" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W20" s="54" t="str">
+      <c r="X20" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-20</v>
       </c>
-      <c r="X20" s="35" t="s">
+      <c r="Y20" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y20" s="35" t="s">
+      <c r="Z20" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA20" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z20" s="50" t="s">
+      <c r="AB20" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC20" s="50" t="s">
         <v>766</v>
       </c>
-      <c r="AA20" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Organization Services</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="46">
         <v>21</v>
       </c>
@@ -6116,47 +6318,51 @@
       <c r="P21" s="49" t="s">
         <v>754</v>
       </c>
-      <c r="Q21" s="35" t="str">
+      <c r="Q21" s="35" t="s">
+        <v>889</v>
+      </c>
+      <c r="R21" s="35" t="s">
+        <v>876</v>
+      </c>
+      <c r="S21" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T21" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Servicios de Desarrollo de Proyectos</v>
-      </c>
-      <c r="R21" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S21" s="50" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T21" s="50" t="str">
-        <f t="shared" si="10"/>
+      <c r="U21" s="50" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U21" s="49" t="str">
-        <f t="shared" si="10"/>
+      <c r="V21" s="49" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V21" s="35" t="s">
+      <c r="W21" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W21" s="54" t="str">
+      <c r="X21" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-21</v>
       </c>
-      <c r="X21" s="35" t="s">
+      <c r="Y21" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y21" s="35" t="s">
+      <c r="Z21" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA21" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z21" s="50" t="s">
+      <c r="AB21" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC21" s="50" t="s">
         <v>763</v>
       </c>
-      <c r="AA21" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Project Development Services</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="46">
         <v>22</v>
       </c>
@@ -6209,47 +6415,51 @@
       <c r="P22" s="49" t="s">
         <v>755</v>
       </c>
-      <c r="Q22" s="35" t="str">
+      <c r="Q22" s="35" t="s">
+        <v>890</v>
+      </c>
+      <c r="R22" s="35" t="s">
+        <v>877</v>
+      </c>
+      <c r="S22" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T22" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Servicios de Documentos</v>
-      </c>
-      <c r="R22" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S22" s="50" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T22" s="50" t="str">
-        <f t="shared" si="10"/>
+      <c r="U22" s="50" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U22" s="49" t="str">
-        <f t="shared" si="10"/>
+      <c r="V22" s="49" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V22" s="35" t="s">
+      <c r="W22" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W22" s="54" t="str">
+      <c r="X22" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-22</v>
       </c>
-      <c r="X22" s="35" t="s">
+      <c r="Y22" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y22" s="35" t="s">
+      <c r="Z22" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA22" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z22" s="50" t="s">
+      <c r="AB22" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC22" s="50" t="s">
         <v>764</v>
       </c>
-      <c r="AA22" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Document Services</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="46">
         <v>23</v>
       </c>
@@ -6302,47 +6512,51 @@
       <c r="P23" s="49" t="s">
         <v>756</v>
       </c>
-      <c r="Q23" s="35" t="str">
+      <c r="Q23" s="35" t="s">
+        <v>891</v>
+      </c>
+      <c r="R23" s="35" t="s">
+        <v>878</v>
+      </c>
+      <c r="S23" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T23" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Servicios de Implementación</v>
-      </c>
-      <c r="R23" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S23" s="50" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T23" s="50" t="str">
-        <f t="shared" si="10"/>
+      <c r="U23" s="50" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U23" s="49" t="str">
-        <f t="shared" si="10"/>
+      <c r="V23" s="49" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V23" s="35" t="s">
+      <c r="W23" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W23" s="54" t="str">
+      <c r="X23" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-23</v>
       </c>
-      <c r="X23" s="35" t="s">
+      <c r="Y23" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y23" s="35" t="s">
+      <c r="Z23" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA23" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z23" s="50" t="s">
+      <c r="AB23" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC23" s="50" t="s">
         <v>767</v>
       </c>
-      <c r="AA23" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Implementation Services</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="46">
         <v>24</v>
       </c>
@@ -6395,47 +6609,51 @@
       <c r="P24" s="49" t="s">
         <v>757</v>
       </c>
-      <c r="Q24" s="35" t="str">
+      <c r="Q24" s="35" t="s">
+        <v>892</v>
+      </c>
+      <c r="R24" s="35" t="s">
+        <v>879</v>
+      </c>
+      <c r="S24" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T24" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Servicios de Operación de Edificios</v>
-      </c>
-      <c r="R24" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S24" s="50" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T24" s="50" t="str">
-        <f t="shared" si="10"/>
+      <c r="U24" s="50" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U24" s="49" t="str">
-        <f t="shared" si="10"/>
+      <c r="V24" s="49" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V24" s="35" t="s">
+      <c r="W24" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W24" s="54" t="str">
+      <c r="X24" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-24</v>
       </c>
-      <c r="X24" s="35" t="s">
+      <c r="Y24" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y24" s="35" t="s">
+      <c r="Z24" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA24" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z24" s="50" t="s">
+      <c r="AB24" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC24" s="50" t="s">
         <v>768</v>
       </c>
-      <c r="AA24" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Building Operation Services</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="46">
         <v>25</v>
       </c>
@@ -6488,47 +6706,51 @@
       <c r="P25" s="49" t="s">
         <v>758</v>
       </c>
-      <c r="Q25" s="35" t="str">
+      <c r="Q25" s="35" t="s">
+        <v>893</v>
+      </c>
+      <c r="R25" s="35" t="s">
+        <v>880</v>
+      </c>
+      <c r="S25" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T25" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Servicios de apoyo</v>
-      </c>
-      <c r="R25" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S25" s="50" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T25" s="50" t="str">
-        <f t="shared" si="10"/>
+      <c r="U25" s="50" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U25" s="49" t="str">
-        <f t="shared" si="10"/>
+      <c r="V25" s="49" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V25" s="35" t="s">
+      <c r="W25" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W25" s="54" t="str">
+      <c r="X25" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-25</v>
       </c>
-      <c r="X25" s="35" t="s">
+      <c r="Y25" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y25" s="35" t="s">
+      <c r="Z25" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA25" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z25" s="50" t="s">
+      <c r="AB25" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC25" s="50" t="s">
         <v>769</v>
       </c>
-      <c r="AA25" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Support Services</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="46">
         <v>26</v>
       </c>
@@ -6581,47 +6803,51 @@
       <c r="P26" s="49" t="s">
         <v>759</v>
       </c>
-      <c r="Q26" s="35" t="str">
+      <c r="Q26" s="35" t="s">
+        <v>894</v>
+      </c>
+      <c r="R26" s="35" t="s">
+        <v>881</v>
+      </c>
+      <c r="S26" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T26" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Servicios gubernamentales</v>
-      </c>
-      <c r="R26" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S26" s="50" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T26" s="50" t="str">
-        <f t="shared" si="10"/>
+      <c r="U26" s="50" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U26" s="49" t="str">
-        <f t="shared" si="10"/>
+      <c r="V26" s="49" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V26" s="35" t="s">
+      <c r="W26" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W26" s="54" t="str">
+      <c r="X26" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-26</v>
       </c>
-      <c r="X26" s="35" t="s">
+      <c r="Y26" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y26" s="35" t="s">
+      <c r="Z26" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA26" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z26" s="50" t="s">
+      <c r="AB26" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC26" s="50" t="s">
         <v>770</v>
       </c>
-      <c r="AA26" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Government Services</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="46">
         <v>27</v>
       </c>
@@ -6674,63 +6900,72 @@
       <c r="P27" s="49" t="s">
         <v>760</v>
       </c>
-      <c r="Q27" s="35" t="str">
+      <c r="Q27" s="35" t="s">
+        <v>895</v>
+      </c>
+      <c r="R27" s="35" t="s">
+        <v>882</v>
+      </c>
+      <c r="S27" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="T27" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Servicios adicionales</v>
-      </c>
-      <c r="R27" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S27" s="50" t="str">
-        <f t="shared" si="10"/>
         <v>Normativos</v>
       </c>
-      <c r="T27" s="50" t="str">
-        <f t="shared" si="10"/>
+      <c r="U27" s="50" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Temáticas</v>
       </c>
-      <c r="U27" s="49" t="str">
-        <f t="shared" si="10"/>
+      <c r="V27" s="49" t="str">
+        <f t="shared" si="8"/>
         <v>NBR.Serviços</v>
       </c>
-      <c r="V27" s="35" t="s">
+      <c r="W27" s="35" t="s">
         <v>705</v>
       </c>
-      <c r="W27" s="54" t="str">
+      <c r="X27" s="54" t="str">
         <f t="shared" si="7"/>
         <v>Key-ABNT-27</v>
       </c>
-      <c r="X27" s="35" t="s">
+      <c r="Y27" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="Y27" s="35" t="s">
+      <c r="Z27" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AA27" s="35" t="s">
         <v>857</v>
       </c>
-      <c r="Z27" s="50" t="s">
+      <c r="AB27" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="AC27" s="50" t="s">
         <v>771</v>
-      </c>
-      <c r="AA27" s="35" t="str">
-        <f t="shared" si="9"/>
-        <v>Additional services</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="19" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y2">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+  <conditionalFormatting sqref="Y2 AA2">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA27 A2:B27">
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B27">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R27">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6745,13 +6980,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEF6990-269C-482F-AEAB-0F771E87FB19}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>657</v>
       </c>
@@ -6816,7 +7051,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -6898,13 +7133,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56C5A03-15CD-4694-84A2-E149E46D665B}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.796875" customWidth="1"/>
+    <col min="2" max="3" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -6915,7 +7150,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -6940,27 +7175,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2864B2AC-DDFD-480C-BEC0-F2615FD9637A}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y305"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.83203125" style="2" customWidth="1"/>
     <col min="4" max="5" width="8" style="2" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.296875" customWidth="1"/>
-    <col min="9" max="9" width="5.69921875" customWidth="1"/>
-    <col min="10" max="10" width="3.69921875" customWidth="1"/>
-    <col min="11" max="11" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" customWidth="1"/>
+    <col min="10" max="10" width="3.6640625" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.5" customWidth="1"/>
     <col min="13" max="13" width="27" customWidth="1"/>
-    <col min="14" max="14" width="6.296875" customWidth="1"/>
+    <col min="14" max="14" width="6.33203125" customWidth="1"/>
     <col min="15" max="15" width="32.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="3.796875" customWidth="1"/>
+    <col min="17" max="17" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="3.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>319</v>
       </c>
@@ -7033,7 +7268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -7110,7 +7345,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -7187,7 +7422,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -7264,7 +7499,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -7341,7 +7576,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -7418,7 +7653,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -7495,7 +7730,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -7572,7 +7807,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -7649,7 +7884,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -7726,7 +7961,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -7803,7 +8038,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -7880,7 +8115,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -7957,7 +8192,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -8034,7 +8269,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -8111,7 +8346,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -8188,7 +8423,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -8265,7 +8500,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -8342,7 +8577,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -8419,7 +8654,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -8496,7 +8731,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -8573,7 +8808,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -8650,7 +8885,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -8727,7 +8962,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -8804,7 +9039,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -8881,7 +9116,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -8958,7 +9193,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -9035,7 +9270,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -9112,7 +9347,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -9189,7 +9424,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -9266,7 +9501,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -9343,7 +9578,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -9420,7 +9655,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -9497,7 +9732,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -9574,7 +9809,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -9651,7 +9886,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -9728,7 +9963,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -9805,7 +10040,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -9882,7 +10117,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -9959,7 +10194,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -10036,7 +10271,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -10113,7 +10348,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -10190,7 +10425,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -10267,7 +10502,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -10344,7 +10579,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -10421,7 +10656,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -10498,7 +10733,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -10575,7 +10810,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -10652,7 +10887,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -10729,7 +10964,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -10806,7 +11041,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -10883,7 +11118,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -10960,7 +11195,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -11037,7 +11272,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -11114,7 +11349,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -11191,7 +11426,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -11268,7 +11503,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -11345,7 +11580,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -11422,7 +11657,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -11499,7 +11734,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -11576,7 +11811,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -11653,7 +11888,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -11730,7 +11965,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -11807,7 +12042,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -11884,7 +12119,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -11961,7 +12196,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -12038,7 +12273,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -12115,7 +12350,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -12192,7 +12427,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -12269,7 +12504,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -12346,7 +12581,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -12423,7 +12658,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -12500,7 +12735,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -12577,7 +12812,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -12654,7 +12889,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -12731,7 +12966,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -12808,7 +13043,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -12885,7 +13120,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -12962,7 +13197,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -13039,7 +13274,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -13116,7 +13351,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -13193,7 +13428,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -13270,7 +13505,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -13347,7 +13582,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -13424,7 +13659,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -13501,7 +13736,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -13578,7 +13813,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -13655,7 +13890,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -13732,7 +13967,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -13809,7 +14044,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -13886,7 +14121,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -13963,7 +14198,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -14040,7 +14275,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -14117,7 +14352,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -14194,7 +14429,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -14271,7 +14506,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -14348,7 +14583,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -14425,7 +14660,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -14502,7 +14737,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -14579,7 +14814,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -14656,7 +14891,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -14733,7 +14968,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -14810,7 +15045,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -14887,7 +15122,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -14964,7 +15199,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -15041,7 +15276,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -15118,7 +15353,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -15195,7 +15430,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -15272,7 +15507,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -15349,7 +15584,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -15426,7 +15661,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -15503,7 +15738,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -15580,7 +15815,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -15657,7 +15892,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -15734,7 +15969,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -15811,7 +16046,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -15888,7 +16123,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -15965,7 +16200,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -16042,7 +16277,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -16119,7 +16354,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -16196,7 +16431,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -16273,7 +16508,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -16350,7 +16585,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -16427,7 +16662,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -16504,7 +16739,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -16581,7 +16816,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -16658,7 +16893,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -16735,7 +16970,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -16812,7 +17047,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -16889,7 +17124,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -16966,7 +17201,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -17043,7 +17278,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -17120,7 +17355,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -17197,7 +17432,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -17274,7 +17509,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -17351,7 +17586,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -17428,7 +17663,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -17505,7 +17740,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -17582,7 +17817,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -17659,7 +17894,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -17736,7 +17971,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -17813,7 +18048,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -17890,7 +18125,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -17967,7 +18202,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -18044,7 +18279,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -18121,7 +18356,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -18198,7 +18433,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -18275,7 +18510,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -18352,7 +18587,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -18429,7 +18664,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -18506,7 +18741,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -18583,7 +18818,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -18660,7 +18895,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -18737,7 +18972,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -18814,7 +19049,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -18891,7 +19126,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -18968,7 +19203,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="9">
         <v>157</v>
       </c>
@@ -19045,7 +19280,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="9">
         <v>158</v>
       </c>
@@ -19122,7 +19357,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="9">
         <v>159</v>
       </c>
@@ -19199,7 +19434,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="9">
         <v>160</v>
       </c>
@@ -19276,7 +19511,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="9">
         <v>161</v>
       </c>
@@ -19353,7 +19588,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="9">
         <v>162</v>
       </c>
@@ -19430,7 +19665,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="9">
         <v>163</v>
       </c>
@@ -19507,7 +19742,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="9">
         <v>164</v>
       </c>
@@ -19584,7 +19819,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="9">
         <v>165</v>
       </c>
@@ -19661,7 +19896,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="9">
         <v>166</v>
       </c>
@@ -19738,7 +19973,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="9">
         <v>167</v>
       </c>
@@ -19815,7 +20050,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="9">
         <v>168</v>
       </c>
@@ -19892,7 +20127,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="9">
         <v>169</v>
       </c>
@@ -19969,7 +20204,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="9">
         <v>170</v>
       </c>
@@ -20046,7 +20281,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="9">
         <v>171</v>
       </c>
@@ -20123,7 +20358,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="9">
         <v>172</v>
       </c>
@@ -20200,7 +20435,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="9">
         <v>173</v>
       </c>
@@ -20277,7 +20512,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="9">
         <v>174</v>
       </c>
@@ -20354,7 +20589,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="9">
         <v>175</v>
       </c>
@@ -20431,7 +20666,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="9">
         <v>176</v>
       </c>
@@ -20508,7 +20743,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="9">
         <v>177</v>
       </c>
@@ -20585,7 +20820,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="9">
         <v>178</v>
       </c>
@@ -20662,7 +20897,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="9">
         <v>179</v>
       </c>
@@ -20739,7 +20974,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="9">
         <v>180</v>
       </c>
@@ -20816,7 +21051,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="9">
         <v>181</v>
       </c>
@@ -20893,7 +21128,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="9">
         <v>182</v>
       </c>
@@ -20970,7 +21205,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="9">
         <v>183</v>
       </c>
@@ -21047,7 +21282,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="9">
         <v>184</v>
       </c>
@@ -21124,7 +21359,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="9">
         <v>185</v>
       </c>
@@ -21201,7 +21436,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="9">
         <v>186</v>
       </c>
@@ -21278,7 +21513,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="9">
         <v>187</v>
       </c>
@@ -21355,7 +21590,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="9">
         <v>188</v>
       </c>
@@ -21432,7 +21667,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="9">
         <v>189</v>
       </c>
@@ -21509,7 +21744,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="9">
         <v>190</v>
       </c>
@@ -21586,7 +21821,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="9">
         <v>191</v>
       </c>
@@ -21663,7 +21898,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="9">
         <v>192</v>
       </c>
@@ -21740,7 +21975,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="9">
         <v>193</v>
       </c>
@@ -21817,7 +22052,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="9">
         <v>194</v>
       </c>
@@ -21894,7 +22129,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="9">
         <v>195</v>
       </c>
@@ -21971,7 +22206,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="9">
         <v>196</v>
       </c>
@@ -22048,7 +22283,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="9">
         <v>197</v>
       </c>
@@ -22125,7 +22360,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="9">
         <v>198</v>
       </c>
@@ -22202,7 +22437,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="9">
         <v>199</v>
       </c>
@@ -22279,7 +22514,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="9">
         <v>200</v>
       </c>
@@ -22356,7 +22591,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="9">
         <v>201</v>
       </c>
@@ -22433,7 +22668,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="9">
         <v>202</v>
       </c>
@@ -22510,7 +22745,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="9">
         <v>203</v>
       </c>
@@ -22587,7 +22822,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="9">
         <v>204</v>
       </c>
@@ -22664,7 +22899,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="9">
         <v>205</v>
       </c>
@@ -22741,7 +22976,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="9">
         <v>206</v>
       </c>
@@ -22818,7 +23053,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="9">
         <v>207</v>
       </c>
@@ -22895,7 +23130,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="9">
         <v>208</v>
       </c>
@@ -22972,7 +23207,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="9">
         <v>209</v>
       </c>
@@ -23049,7 +23284,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="9">
         <v>210</v>
       </c>
@@ -23126,7 +23361,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="9">
         <v>211</v>
       </c>
@@ -23203,7 +23438,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="9">
         <v>212</v>
       </c>
@@ -23280,7 +23515,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="9">
         <v>213</v>
       </c>
@@ -23357,7 +23592,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="9">
         <v>214</v>
       </c>
@@ -23434,7 +23669,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="9">
         <v>215</v>
       </c>
@@ -23511,7 +23746,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="9">
         <v>216</v>
       </c>
@@ -23588,7 +23823,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="9">
         <v>217</v>
       </c>
@@ -23665,7 +23900,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="9">
         <v>218</v>
       </c>
@@ -23742,7 +23977,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="9">
         <v>219</v>
       </c>
@@ -23819,7 +24054,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="9">
         <v>220</v>
       </c>
@@ -23896,7 +24131,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="9">
         <v>221</v>
       </c>
@@ -23973,7 +24208,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="9">
         <v>222</v>
       </c>
@@ -24050,7 +24285,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="9">
         <v>223</v>
       </c>
@@ -24127,7 +24362,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="9">
         <v>224</v>
       </c>
@@ -24204,7 +24439,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="9">
         <v>225</v>
       </c>
@@ -24281,7 +24516,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="9">
         <v>226</v>
       </c>
@@ -24358,7 +24593,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="9">
         <v>227</v>
       </c>
@@ -24435,7 +24670,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="9">
         <v>228</v>
       </c>
@@ -24512,7 +24747,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="9">
         <v>229</v>
       </c>
@@ -24589,7 +24824,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="9">
         <v>230</v>
       </c>
@@ -24666,7 +24901,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="9">
         <v>231</v>
       </c>
@@ -24743,7 +24978,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="9">
         <v>232</v>
       </c>
@@ -24820,7 +25055,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="9">
         <v>233</v>
       </c>
@@ -24897,7 +25132,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="9">
         <v>234</v>
       </c>
@@ -24974,7 +25209,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="9">
         <v>235</v>
       </c>
@@ -25051,7 +25286,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="9">
         <v>236</v>
       </c>
@@ -25128,7 +25363,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="9">
         <v>237</v>
       </c>
@@ -25205,7 +25440,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="9">
         <v>238</v>
       </c>
@@ -25282,7 +25517,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="9">
         <v>239</v>
       </c>
@@ -25359,7 +25594,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="9">
         <v>240</v>
       </c>
@@ -25436,7 +25671,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="9">
         <v>241</v>
       </c>
@@ -25513,7 +25748,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="9">
         <v>242</v>
       </c>
@@ -25590,7 +25825,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="9">
         <v>243</v>
       </c>
@@ -25667,7 +25902,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="9">
         <v>244</v>
       </c>
@@ -25744,7 +25979,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="9">
         <v>245</v>
       </c>
@@ -25821,7 +26056,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="9">
         <v>246</v>
       </c>
@@ -25898,7 +26133,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="9">
         <v>247</v>
       </c>
@@ -25975,7 +26210,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="9">
         <v>248</v>
       </c>
@@ -26052,7 +26287,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="9">
         <v>249</v>
       </c>
@@ -26129,7 +26364,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="9">
         <v>250</v>
       </c>
@@ -26206,7 +26441,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="9">
         <v>251</v>
       </c>
@@ -26283,7 +26518,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="9">
         <v>252</v>
       </c>
@@ -26360,7 +26595,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="9">
         <v>253</v>
       </c>
@@ -26437,7 +26672,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="9">
         <v>254</v>
       </c>
@@ -26514,7 +26749,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="9">
         <v>255</v>
       </c>
@@ -26591,7 +26826,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="9">
         <v>256</v>
       </c>
@@ -26668,7 +26903,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="9">
         <v>257</v>
       </c>
@@ -26745,7 +26980,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="9">
         <v>258</v>
       </c>
@@ -26822,7 +27057,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="9">
         <v>259</v>
       </c>
@@ -26899,7 +27134,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="9">
         <v>260</v>
       </c>
@@ -26976,7 +27211,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="9">
         <v>261</v>
       </c>
@@ -27053,7 +27288,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="9">
         <v>262</v>
       </c>
@@ -27130,7 +27365,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="9">
         <v>263</v>
       </c>
@@ -27207,7 +27442,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="9">
         <v>264</v>
       </c>
@@ -27284,7 +27519,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="9">
         <v>265</v>
       </c>
@@ -27361,7 +27596,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="9">
         <v>266</v>
       </c>
@@ -27438,7 +27673,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="9">
         <v>267</v>
       </c>
@@ -27515,7 +27750,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="9">
         <v>268</v>
       </c>
@@ -27592,7 +27827,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="9">
         <v>269</v>
       </c>
@@ -27669,7 +27904,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="9">
         <v>270</v>
       </c>
@@ -27746,7 +27981,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="9">
         <v>271</v>
       </c>
@@ -27823,7 +28058,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="9">
         <v>272</v>
       </c>
@@ -27900,7 +28135,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="9">
         <v>273</v>
       </c>
@@ -27977,7 +28212,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="9">
         <v>274</v>
       </c>
@@ -28054,7 +28289,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="9">
         <v>275</v>
       </c>
@@ -28131,7 +28366,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="9">
         <v>276</v>
       </c>
@@ -28208,7 +28443,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="9">
         <v>277</v>
       </c>
@@ -28285,7 +28520,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="9">
         <v>278</v>
       </c>
@@ -28362,7 +28597,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="9">
         <v>279</v>
       </c>
@@ -28439,7 +28674,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="9">
         <v>280</v>
       </c>
@@ -28516,7 +28751,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="9">
         <v>281</v>
       </c>
@@ -28593,7 +28828,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="9">
         <v>282</v>
       </c>
@@ -28670,7 +28905,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="9">
         <v>283</v>
       </c>
@@ -28747,7 +28982,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="9">
         <v>284</v>
       </c>
@@ -28824,7 +29059,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="9">
         <v>285</v>
       </c>
@@ -28901,7 +29136,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="9">
         <v>286</v>
       </c>
@@ -28978,7 +29213,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="9">
         <v>287</v>
       </c>
@@ -29055,7 +29290,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="9">
         <v>288</v>
       </c>
@@ -29132,7 +29367,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="9">
         <v>289</v>
       </c>
@@ -29209,7 +29444,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="9">
         <v>290</v>
       </c>
@@ -29286,7 +29521,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="9">
         <v>291</v>
       </c>
@@ -29363,7 +29598,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="9">
         <v>292</v>
       </c>
@@ -29440,7 +29675,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="9">
         <v>293</v>
       </c>
@@ -29517,7 +29752,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="9">
         <v>294</v>
       </c>
@@ -29594,7 +29829,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="9">
         <v>295</v>
       </c>
@@ -29671,7 +29906,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="9">
         <v>296</v>
       </c>
@@ -29748,7 +29983,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="9">
         <v>297</v>
       </c>
@@ -29825,7 +30060,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="9">
         <v>298</v>
       </c>
@@ -29902,7 +30137,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="9">
         <v>299</v>
       </c>
@@ -29979,7 +30214,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="9">
         <v>300</v>
       </c>
@@ -30056,7 +30291,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="9">
         <v>301</v>
       </c>
@@ -30133,7 +30368,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="9">
         <v>302</v>
       </c>
@@ -30210,7 +30445,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="9">
         <v>303</v>
       </c>
@@ -30287,7 +30522,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="9">
         <v>304</v>
       </c>
@@ -30364,7 +30599,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="9">
         <v>305</v>
       </c>

--- a/Versão5/ABNT/Ontologia_NBR15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1S.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78830A76-B747-4250-BAE8-00452A8CE6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7A4BC5-B3A7-4D5F-8BB7-8067A0163412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10645" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10640" uniqueCount="926">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2853,19 +2853,22 @@
     <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
   </si>
   <si>
-    <t>é.rvt.ambiente</t>
-  </si>
-  <si>
-    <t>é.rvt.andar</t>
-  </si>
-  <si>
-    <t>é.rvt.elemento</t>
-  </si>
-  <si>
-    <t>é.rvt.tipo</t>
-  </si>
-  <si>
-    <t>é.rvt.material</t>
+    <t>é.selecionado.por</t>
+  </si>
+  <si>
+    <t>"[ FilteredElementCollector(doc).OfClass(typeof(SpatialElement)).Cast&lt;SpatialElement&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
+  </si>
+  <si>
+    <t>"[ FilteredElementCollector(doc).OfClass(typeof(Level)).Cast&lt;Level&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
+  </si>
+  <si>
+    <t>"[ EleBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilyInstance)).Cast&lt;FamilyInstance&gt;().FirstOrDefault( e =&gt; e.Symbol.Name == 'InsBuscada') ]"</t>
+  </si>
+  <si>
+    <t>"[ TipBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilySymbol )).Cast&lt;FamilySymbol&gt;( ).FirstOrDefault( e =&gt; e.Name        == 'TipBuscado') ]"</t>
+  </si>
+  <si>
+    <t>"[ MtlBuscado : FilteredElementCollector(doc).OfClass(typeof(Material)).Cast&lt;Material&gt;( ).FirstOrDefault( e =&gt; e.Name  == 'MtlBuscado') ]"</t>
   </si>
 </sst>
 </file>
@@ -2987,7 +2990,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="29">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3156,6 +3159,18 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -3223,7 +3238,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3418,59 +3433,25 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{75D7255F-4B16-4C61-A12B-6DBA4ACA1970}"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="31">
     <dxf>
       <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0"/>
       </font>
     </dxf>
     <dxf>
@@ -3502,7 +3483,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -4269,7 +4250,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46257.697396527779</v>
+        <v>46257.755616435184</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>689</v>
@@ -7263,29 +7244,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B28">
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F14">
-    <cfRule type="duplicateValues" dxfId="34" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="33" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="duplicateValues" dxfId="29" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R28">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2 AA2">
-    <cfRule type="cellIs" dxfId="27" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7438,7 +7419,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7483,7 +7464,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7513,22 +7494,22 @@
     <col min="14" max="14" width="5.3984375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="43.3984375" style="32" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="80.59765625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5.09765625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3.69921875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.09765625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3.69921875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="3.09765625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.796875" customWidth="1"/>
     <col min="25" max="25" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.796875" customWidth="1"/>
     <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.796875" customWidth="1"/>
     <col min="29" max="29" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.8984375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.796875" customWidth="1"/>
     <col min="31" max="31" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.796875" customWidth="1"/>
     <col min="33" max="33" width="7.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7908,25 +7889,25 @@
         <v>904</v>
       </c>
       <c r="Z4" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA4" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB4" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC4" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD4" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE4" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF4" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG4" s="53" t="s">
         <v>917</v>
@@ -8009,25 +7990,25 @@
         <v>904</v>
       </c>
       <c r="Z5" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA5" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB5" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC5" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD5" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE5" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF5" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG5" s="53" t="s">
         <v>917</v>
@@ -8110,25 +8091,25 @@
         <v>904</v>
       </c>
       <c r="Z6" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA6" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB6" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC6" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD6" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE6" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF6" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG6" s="53" t="s">
         <v>917</v>
@@ -8211,25 +8192,25 @@
         <v>904</v>
       </c>
       <c r="Z7" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA7" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB7" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC7" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD7" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE7" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF7" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG7" s="53" t="s">
         <v>917</v>
@@ -8312,25 +8293,25 @@
         <v>904</v>
       </c>
       <c r="Z8" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA8" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB8" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC8" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD8" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE8" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF8" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG8" s="53" t="s">
         <v>917</v>
@@ -8413,25 +8394,25 @@
         <v>904</v>
       </c>
       <c r="Z9" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA9" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB9" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC9" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD9" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE9" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF9" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG9" s="53" t="s">
         <v>917</v>
@@ -8514,25 +8495,25 @@
         <v>904</v>
       </c>
       <c r="Z10" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA10" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB10" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC10" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD10" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE10" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF10" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG10" s="53" t="s">
         <v>917</v>
@@ -8615,25 +8596,25 @@
         <v>904</v>
       </c>
       <c r="Z11" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA11" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB11" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC11" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD11" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE11" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF11" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG11" s="53" t="s">
         <v>917</v>
@@ -8716,25 +8697,25 @@
         <v>904</v>
       </c>
       <c r="Z12" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA12" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB12" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC12" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD12" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE12" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF12" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG12" s="53" t="s">
         <v>917</v>
@@ -8817,25 +8798,25 @@
         <v>904</v>
       </c>
       <c r="Z13" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA13" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB13" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC13" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD13" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE13" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF13" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG13" s="53" t="s">
         <v>917</v>
@@ -8918,25 +8899,25 @@
         <v>904</v>
       </c>
       <c r="Z14" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA14" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB14" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC14" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD14" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE14" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF14" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG14" s="53" t="s">
         <v>917</v>
@@ -9019,25 +9000,25 @@
         <v>904</v>
       </c>
       <c r="Z15" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA15" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB15" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC15" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD15" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE15" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF15" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG15" s="53" t="s">
         <v>917</v>
@@ -9120,25 +9101,25 @@
         <v>904</v>
       </c>
       <c r="Z16" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA16" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB16" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC16" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD16" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE16" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF16" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG16" s="53" t="s">
         <v>917</v>
@@ -9221,25 +9202,25 @@
         <v>904</v>
       </c>
       <c r="Z17" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA17" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB17" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC17" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD17" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE17" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF17" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG17" s="53" t="s">
         <v>917</v>
@@ -9322,25 +9303,25 @@
         <v>904</v>
       </c>
       <c r="Z18" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA18" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB18" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC18" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD18" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE18" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF18" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG18" s="53" t="s">
         <v>917</v>
@@ -9423,25 +9404,25 @@
         <v>904</v>
       </c>
       <c r="Z19" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA19" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB19" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC19" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD19" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE19" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF19" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG19" s="53" t="s">
         <v>917</v>
@@ -9524,25 +9505,25 @@
         <v>904</v>
       </c>
       <c r="Z20" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA20" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB20" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC20" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD20" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE20" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF20" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG20" s="53" t="s">
         <v>917</v>
@@ -9625,25 +9606,25 @@
         <v>904</v>
       </c>
       <c r="Z21" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA21" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB21" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC21" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD21" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE21" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF21" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG21" s="53" t="s">
         <v>917</v>
@@ -9726,25 +9707,25 @@
         <v>904</v>
       </c>
       <c r="Z22" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA22" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB22" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC22" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD22" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE22" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF22" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG22" s="53" t="s">
         <v>917</v>
@@ -9827,25 +9808,25 @@
         <v>904</v>
       </c>
       <c r="Z23" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA23" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB23" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC23" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD23" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE23" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF23" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG23" s="53" t="s">
         <v>917</v>
@@ -9928,25 +9909,25 @@
         <v>904</v>
       </c>
       <c r="Z24" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA24" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB24" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC24" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD24" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE24" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF24" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG24" s="53" t="s">
         <v>917</v>
@@ -10029,25 +10010,25 @@
         <v>904</v>
       </c>
       <c r="Z25" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA25" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB25" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC25" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD25" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE25" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF25" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG25" s="53" t="s">
         <v>917</v>
@@ -10130,25 +10111,25 @@
         <v>904</v>
       </c>
       <c r="Z26" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA26" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB26" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC26" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD26" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE26" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF26" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG26" s="53" t="s">
         <v>917</v>
@@ -10231,25 +10212,25 @@
         <v>904</v>
       </c>
       <c r="Z27" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA27" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB27" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC27" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD27" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE27" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF27" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG27" s="53" t="s">
         <v>917</v>
@@ -10332,25 +10313,25 @@
         <v>904</v>
       </c>
       <c r="Z28" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA28" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB28" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC28" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD28" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE28" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF28" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG28" s="53" t="s">
         <v>917</v>
@@ -10433,25 +10414,25 @@
         <v>904</v>
       </c>
       <c r="Z29" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA29" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB29" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC29" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD29" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE29" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF29" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG29" s="53" t="s">
         <v>917</v>
@@ -10534,25 +10515,25 @@
         <v>904</v>
       </c>
       <c r="Z30" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA30" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB30" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC30" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD30" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE30" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF30" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG30" s="53" t="s">
         <v>917</v>
@@ -10635,25 +10616,25 @@
         <v>904</v>
       </c>
       <c r="Z31" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA31" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB31" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC31" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD31" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE31" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF31" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG31" s="53" t="s">
         <v>917</v>
@@ -10736,25 +10717,25 @@
         <v>904</v>
       </c>
       <c r="Z32" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA32" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB32" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC32" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD32" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE32" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF32" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG32" s="53" t="s">
         <v>917</v>
@@ -10837,25 +10818,25 @@
         <v>904</v>
       </c>
       <c r="Z33" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA33" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB33" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC33" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD33" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE33" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF33" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG33" s="53" t="s">
         <v>917</v>
@@ -10938,25 +10919,25 @@
         <v>904</v>
       </c>
       <c r="Z34" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA34" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB34" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC34" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD34" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE34" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF34" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG34" s="53" t="s">
         <v>917</v>
@@ -11039,25 +11020,25 @@
         <v>904</v>
       </c>
       <c r="Z35" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA35" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB35" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC35" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD35" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE35" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF35" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG35" s="53" t="s">
         <v>917</v>
@@ -11140,25 +11121,25 @@
         <v>904</v>
       </c>
       <c r="Z36" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA36" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB36" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC36" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD36" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE36" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF36" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG36" s="53" t="s">
         <v>917</v>
@@ -11241,25 +11222,25 @@
         <v>904</v>
       </c>
       <c r="Z37" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA37" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB37" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC37" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD37" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE37" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF37" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG37" s="53" t="s">
         <v>917</v>
@@ -11342,25 +11323,25 @@
         <v>904</v>
       </c>
       <c r="Z38" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA38" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB38" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC38" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD38" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE38" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF38" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG38" s="53" t="s">
         <v>917</v>
@@ -11443,25 +11424,25 @@
         <v>904</v>
       </c>
       <c r="Z39" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA39" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB39" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC39" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD39" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE39" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF39" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG39" s="53" t="s">
         <v>917</v>
@@ -11544,25 +11525,25 @@
         <v>904</v>
       </c>
       <c r="Z40" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA40" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB40" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC40" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD40" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE40" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF40" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG40" s="53" t="s">
         <v>917</v>
@@ -11645,25 +11626,25 @@
         <v>904</v>
       </c>
       <c r="Z41" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA41" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB41" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC41" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD41" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE41" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF41" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG41" s="53" t="s">
         <v>917</v>
@@ -11746,25 +11727,25 @@
         <v>904</v>
       </c>
       <c r="Z42" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA42" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB42" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC42" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD42" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE42" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF42" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG42" s="53" t="s">
         <v>917</v>
@@ -11847,25 +11828,25 @@
         <v>904</v>
       </c>
       <c r="Z43" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA43" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB43" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC43" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD43" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE43" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF43" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG43" s="53" t="s">
         <v>917</v>
@@ -11948,25 +11929,25 @@
         <v>904</v>
       </c>
       <c r="Z44" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA44" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB44" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC44" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD44" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE44" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF44" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG44" s="53" t="s">
         <v>917</v>
@@ -12049,25 +12030,25 @@
         <v>904</v>
       </c>
       <c r="Z45" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA45" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB45" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC45" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD45" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE45" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF45" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG45" s="53" t="s">
         <v>917</v>
@@ -12150,25 +12131,25 @@
         <v>904</v>
       </c>
       <c r="Z46" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA46" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB46" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC46" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD46" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE46" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF46" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG46" s="53" t="s">
         <v>917</v>
@@ -12251,25 +12232,25 @@
         <v>904</v>
       </c>
       <c r="Z47" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA47" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB47" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC47" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD47" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE47" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF47" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG47" s="53" t="s">
         <v>917</v>
@@ -12352,25 +12333,25 @@
         <v>904</v>
       </c>
       <c r="Z48" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA48" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB48" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC48" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD48" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE48" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF48" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG48" s="53" t="s">
         <v>917</v>
@@ -12453,25 +12434,25 @@
         <v>904</v>
       </c>
       <c r="Z49" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA49" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB49" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC49" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD49" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE49" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF49" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG49" s="53" t="s">
         <v>917</v>
@@ -12554,25 +12535,25 @@
         <v>904</v>
       </c>
       <c r="Z50" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA50" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB50" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC50" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD50" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE50" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF50" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG50" s="53" t="s">
         <v>917</v>
@@ -12655,25 +12636,25 @@
         <v>904</v>
       </c>
       <c r="Z51" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA51" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB51" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC51" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD51" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE51" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF51" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG51" s="53" t="s">
         <v>917</v>
@@ -12756,25 +12737,25 @@
         <v>904</v>
       </c>
       <c r="Z52" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA52" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB52" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC52" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD52" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE52" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF52" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG52" s="53" t="s">
         <v>917</v>
@@ -12857,25 +12838,25 @@
         <v>904</v>
       </c>
       <c r="Z53" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA53" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB53" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC53" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD53" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE53" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF53" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG53" s="53" t="s">
         <v>917</v>
@@ -12958,25 +12939,25 @@
         <v>904</v>
       </c>
       <c r="Z54" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA54" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB54" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC54" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD54" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE54" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF54" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG54" s="53" t="s">
         <v>917</v>
@@ -13059,25 +13040,25 @@
         <v>904</v>
       </c>
       <c r="Z55" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA55" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB55" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC55" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD55" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE55" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF55" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG55" s="53" t="s">
         <v>917</v>
@@ -13160,25 +13141,25 @@
         <v>904</v>
       </c>
       <c r="Z56" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA56" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB56" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC56" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD56" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE56" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF56" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG56" s="53" t="s">
         <v>917</v>
@@ -13261,25 +13242,25 @@
         <v>904</v>
       </c>
       <c r="Z57" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA57" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB57" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC57" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD57" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE57" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF57" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG57" s="53" t="s">
         <v>917</v>
@@ -13362,25 +13343,25 @@
         <v>904</v>
       </c>
       <c r="Z58" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA58" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB58" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC58" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD58" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE58" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF58" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG58" s="53" t="s">
         <v>917</v>
@@ -13463,25 +13444,25 @@
         <v>904</v>
       </c>
       <c r="Z59" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA59" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB59" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC59" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD59" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE59" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF59" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG59" s="53" t="s">
         <v>917</v>
@@ -13564,25 +13545,25 @@
         <v>904</v>
       </c>
       <c r="Z60" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA60" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB60" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC60" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD60" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE60" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF60" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG60" s="53" t="s">
         <v>917</v>
@@ -13665,25 +13646,25 @@
         <v>904</v>
       </c>
       <c r="Z61" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA61" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB61" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC61" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD61" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE61" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF61" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG61" s="53" t="s">
         <v>917</v>
@@ -13766,25 +13747,25 @@
         <v>904</v>
       </c>
       <c r="Z62" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA62" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB62" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC62" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD62" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE62" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF62" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG62" s="53" t="s">
         <v>917</v>
@@ -13867,25 +13848,25 @@
         <v>904</v>
       </c>
       <c r="Z63" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA63" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB63" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC63" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD63" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE63" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF63" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG63" s="53" t="s">
         <v>917</v>
@@ -13968,25 +13949,25 @@
         <v>904</v>
       </c>
       <c r="Z64" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA64" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB64" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC64" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD64" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE64" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF64" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG64" s="53" t="s">
         <v>917</v>
@@ -14069,25 +14050,25 @@
         <v>904</v>
       </c>
       <c r="Z65" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA65" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB65" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC65" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD65" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE65" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF65" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG65" s="53" t="s">
         <v>917</v>
@@ -14170,25 +14151,25 @@
         <v>904</v>
       </c>
       <c r="Z66" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA66" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB66" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC66" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD66" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE66" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF66" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG66" s="53" t="s">
         <v>917</v>
@@ -14271,25 +14252,25 @@
         <v>904</v>
       </c>
       <c r="Z67" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA67" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB67" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC67" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD67" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE67" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF67" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG67" s="53" t="s">
         <v>917</v>
@@ -14372,25 +14353,25 @@
         <v>904</v>
       </c>
       <c r="Z68" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA68" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB68" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC68" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD68" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE68" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF68" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG68" s="53" t="s">
         <v>917</v>
@@ -14473,25 +14454,25 @@
         <v>904</v>
       </c>
       <c r="Z69" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA69" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB69" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC69" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD69" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE69" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF69" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG69" s="53" t="s">
         <v>917</v>
@@ -14574,25 +14555,25 @@
         <v>904</v>
       </c>
       <c r="Z70" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA70" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB70" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC70" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD70" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE70" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF70" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG70" s="53" t="s">
         <v>917</v>
@@ -14675,25 +14656,25 @@
         <v>904</v>
       </c>
       <c r="Z71" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA71" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB71" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC71" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD71" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE71" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF71" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG71" s="53" t="s">
         <v>917</v>
@@ -14776,25 +14757,25 @@
         <v>904</v>
       </c>
       <c r="Z72" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA72" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB72" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC72" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD72" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE72" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF72" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG72" s="53" t="s">
         <v>917</v>
@@ -14877,25 +14858,25 @@
         <v>904</v>
       </c>
       <c r="Z73" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA73" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB73" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC73" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD73" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE73" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF73" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG73" s="53" t="s">
         <v>917</v>
@@ -14978,25 +14959,25 @@
         <v>904</v>
       </c>
       <c r="Z74" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA74" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB74" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC74" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD74" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE74" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF74" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG74" s="53" t="s">
         <v>917</v>
@@ -15079,25 +15060,25 @@
         <v>904</v>
       </c>
       <c r="Z75" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA75" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB75" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC75" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD75" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE75" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF75" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG75" s="53" t="s">
         <v>917</v>
@@ -15180,25 +15161,25 @@
         <v>904</v>
       </c>
       <c r="Z76" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA76" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB76" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC76" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD76" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE76" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF76" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG76" s="53" t="s">
         <v>917</v>
@@ -15281,25 +15262,25 @@
         <v>904</v>
       </c>
       <c r="Z77" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA77" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB77" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC77" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD77" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE77" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF77" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG77" s="53" t="s">
         <v>917</v>
@@ -15382,25 +15363,25 @@
         <v>904</v>
       </c>
       <c r="Z78" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA78" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB78" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC78" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD78" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE78" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF78" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG78" s="53" t="s">
         <v>917</v>
@@ -15483,25 +15464,25 @@
         <v>904</v>
       </c>
       <c r="Z79" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA79" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB79" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC79" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD79" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE79" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF79" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG79" s="53" t="s">
         <v>917</v>
@@ -15584,25 +15565,25 @@
         <v>904</v>
       </c>
       <c r="Z80" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA80" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB80" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC80" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD80" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE80" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF80" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG80" s="53" t="s">
         <v>917</v>
@@ -15685,25 +15666,25 @@
         <v>904</v>
       </c>
       <c r="Z81" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA81" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB81" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC81" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD81" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE81" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF81" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG81" s="53" t="s">
         <v>917</v>
@@ -15786,25 +15767,25 @@
         <v>904</v>
       </c>
       <c r="Z82" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA82" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB82" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC82" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD82" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE82" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF82" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG82" s="53" t="s">
         <v>917</v>
@@ -15887,25 +15868,25 @@
         <v>904</v>
       </c>
       <c r="Z83" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA83" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB83" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC83" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD83" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE83" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF83" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG83" s="53" t="s">
         <v>917</v>
@@ -15988,25 +15969,25 @@
         <v>904</v>
       </c>
       <c r="Z84" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA84" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB84" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC84" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD84" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE84" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF84" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG84" s="53" t="s">
         <v>917</v>
@@ -16089,25 +16070,25 @@
         <v>904</v>
       </c>
       <c r="Z85" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA85" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB85" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC85" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD85" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE85" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF85" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG85" s="53" t="s">
         <v>917</v>
@@ -16190,25 +16171,25 @@
         <v>904</v>
       </c>
       <c r="Z86" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA86" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB86" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC86" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD86" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE86" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF86" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG86" s="53" t="s">
         <v>917</v>
@@ -16291,25 +16272,25 @@
         <v>904</v>
       </c>
       <c r="Z87" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA87" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB87" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC87" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD87" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE87" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF87" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG87" s="53" t="s">
         <v>917</v>
@@ -16392,25 +16373,25 @@
         <v>904</v>
       </c>
       <c r="Z88" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA88" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB88" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC88" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD88" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE88" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF88" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG88" s="53" t="s">
         <v>917</v>
@@ -16493,25 +16474,25 @@
         <v>904</v>
       </c>
       <c r="Z89" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA89" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB89" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC89" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD89" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE89" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF89" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG89" s="53" t="s">
         <v>917</v>
@@ -16594,25 +16575,25 @@
         <v>904</v>
       </c>
       <c r="Z90" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA90" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB90" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC90" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD90" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE90" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF90" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG90" s="53" t="s">
         <v>917</v>
@@ -16695,25 +16676,25 @@
         <v>904</v>
       </c>
       <c r="Z91" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA91" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB91" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC91" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD91" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE91" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF91" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG91" s="53" t="s">
         <v>917</v>
@@ -16796,25 +16777,25 @@
         <v>904</v>
       </c>
       <c r="Z92" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA92" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB92" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC92" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD92" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE92" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF92" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG92" s="53" t="s">
         <v>917</v>
@@ -16897,25 +16878,25 @@
         <v>904</v>
       </c>
       <c r="Z93" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA93" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB93" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC93" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD93" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE93" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF93" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG93" s="53" t="s">
         <v>917</v>
@@ -16998,25 +16979,25 @@
         <v>904</v>
       </c>
       <c r="Z94" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA94" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB94" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC94" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD94" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE94" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF94" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG94" s="53" t="s">
         <v>917</v>
@@ -17099,25 +17080,25 @@
         <v>904</v>
       </c>
       <c r="Z95" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA95" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB95" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC95" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD95" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE95" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF95" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG95" s="53" t="s">
         <v>917</v>
@@ -17200,25 +17181,25 @@
         <v>904</v>
       </c>
       <c r="Z96" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA96" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB96" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC96" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD96" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE96" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF96" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG96" s="53" t="s">
         <v>917</v>
@@ -17301,25 +17282,25 @@
         <v>904</v>
       </c>
       <c r="Z97" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA97" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB97" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC97" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD97" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE97" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF97" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG97" s="53" t="s">
         <v>917</v>
@@ -17402,25 +17383,25 @@
         <v>904</v>
       </c>
       <c r="Z98" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA98" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB98" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC98" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD98" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE98" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF98" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG98" s="53" t="s">
         <v>917</v>
@@ -17503,25 +17484,25 @@
         <v>904</v>
       </c>
       <c r="Z99" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA99" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB99" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC99" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD99" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE99" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF99" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG99" s="53" t="s">
         <v>917</v>
@@ -17604,25 +17585,25 @@
         <v>904</v>
       </c>
       <c r="Z100" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA100" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB100" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC100" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD100" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE100" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF100" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG100" s="53" t="s">
         <v>917</v>
@@ -17705,25 +17686,25 @@
         <v>904</v>
       </c>
       <c r="Z101" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA101" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB101" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC101" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD101" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE101" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF101" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG101" s="53" t="s">
         <v>917</v>
@@ -17806,25 +17787,25 @@
         <v>904</v>
       </c>
       <c r="Z102" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA102" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB102" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC102" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD102" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE102" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF102" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG102" s="53" t="s">
         <v>917</v>
@@ -17907,25 +17888,25 @@
         <v>904</v>
       </c>
       <c r="Z103" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA103" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB103" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC103" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD103" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE103" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF103" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG103" s="53" t="s">
         <v>917</v>
@@ -18008,25 +17989,25 @@
         <v>904</v>
       </c>
       <c r="Z104" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA104" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB104" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC104" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD104" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE104" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF104" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG104" s="53" t="s">
         <v>917</v>
@@ -18109,25 +18090,25 @@
         <v>904</v>
       </c>
       <c r="Z105" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA105" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB105" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC105" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD105" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE105" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF105" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG105" s="53" t="s">
         <v>917</v>
@@ -18210,25 +18191,25 @@
         <v>904</v>
       </c>
       <c r="Z106" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA106" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB106" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC106" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD106" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE106" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF106" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG106" s="53" t="s">
         <v>917</v>
@@ -18311,25 +18292,25 @@
         <v>904</v>
       </c>
       <c r="Z107" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA107" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB107" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC107" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD107" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE107" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF107" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG107" s="53" t="s">
         <v>917</v>
@@ -18412,25 +18393,25 @@
         <v>904</v>
       </c>
       <c r="Z108" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA108" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB108" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC108" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD108" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE108" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF108" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG108" s="53" t="s">
         <v>917</v>
@@ -18513,25 +18494,25 @@
         <v>904</v>
       </c>
       <c r="Z109" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA109" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB109" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC109" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD109" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE109" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF109" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG109" s="53" t="s">
         <v>917</v>
@@ -18614,25 +18595,25 @@
         <v>904</v>
       </c>
       <c r="Z110" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA110" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB110" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC110" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD110" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE110" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF110" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG110" s="53" t="s">
         <v>917</v>
@@ -18715,25 +18696,25 @@
         <v>904</v>
       </c>
       <c r="Z111" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA111" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB111" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC111" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD111" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE111" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF111" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG111" s="53" t="s">
         <v>917</v>
@@ -18816,25 +18797,25 @@
         <v>904</v>
       </c>
       <c r="Z112" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA112" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB112" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC112" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD112" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE112" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF112" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG112" s="53" t="s">
         <v>917</v>
@@ -18917,25 +18898,25 @@
         <v>904</v>
       </c>
       <c r="Z113" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA113" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB113" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC113" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD113" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE113" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF113" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG113" s="53" t="s">
         <v>917</v>
@@ -19018,25 +18999,25 @@
         <v>904</v>
       </c>
       <c r="Z114" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA114" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB114" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC114" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD114" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE114" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF114" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG114" s="53" t="s">
         <v>917</v>
@@ -19119,25 +19100,25 @@
         <v>904</v>
       </c>
       <c r="Z115" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA115" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB115" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC115" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD115" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE115" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF115" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG115" s="53" t="s">
         <v>917</v>
@@ -19220,25 +19201,25 @@
         <v>904</v>
       </c>
       <c r="Z116" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA116" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB116" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC116" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD116" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE116" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF116" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG116" s="53" t="s">
         <v>917</v>
@@ -19321,25 +19302,25 @@
         <v>904</v>
       </c>
       <c r="Z117" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA117" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB117" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC117" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD117" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE117" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF117" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG117" s="53" t="s">
         <v>917</v>
@@ -19422,25 +19403,25 @@
         <v>904</v>
       </c>
       <c r="Z118" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA118" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB118" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC118" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD118" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE118" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF118" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG118" s="53" t="s">
         <v>917</v>
@@ -19523,25 +19504,25 @@
         <v>904</v>
       </c>
       <c r="Z119" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA119" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB119" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC119" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD119" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE119" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF119" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG119" s="53" t="s">
         <v>917</v>
@@ -19624,25 +19605,25 @@
         <v>904</v>
       </c>
       <c r="Z120" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA120" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB120" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC120" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD120" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE120" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF120" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG120" s="53" t="s">
         <v>917</v>
@@ -19725,25 +19706,25 @@
         <v>904</v>
       </c>
       <c r="Z121" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA121" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB121" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC121" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD121" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE121" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF121" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG121" s="53" t="s">
         <v>917</v>
@@ -19826,25 +19807,25 @@
         <v>904</v>
       </c>
       <c r="Z122" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA122" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB122" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC122" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD122" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE122" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF122" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG122" s="53" t="s">
         <v>917</v>
@@ -19927,25 +19908,25 @@
         <v>904</v>
       </c>
       <c r="Z123" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA123" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB123" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC123" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD123" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE123" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF123" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG123" s="53" t="s">
         <v>917</v>
@@ -20028,25 +20009,25 @@
         <v>904</v>
       </c>
       <c r="Z124" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA124" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB124" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC124" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD124" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE124" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF124" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG124" s="53" t="s">
         <v>917</v>
@@ -20129,25 +20110,25 @@
         <v>904</v>
       </c>
       <c r="Z125" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA125" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB125" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC125" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD125" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE125" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF125" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG125" s="53" t="s">
         <v>917</v>
@@ -20230,25 +20211,25 @@
         <v>904</v>
       </c>
       <c r="Z126" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA126" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB126" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC126" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD126" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE126" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF126" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG126" s="53" t="s">
         <v>917</v>
@@ -20331,25 +20312,25 @@
         <v>904</v>
       </c>
       <c r="Z127" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA127" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB127" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC127" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD127" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE127" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF127" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG127" s="53" t="s">
         <v>917</v>
@@ -20432,25 +20413,25 @@
         <v>904</v>
       </c>
       <c r="Z128" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA128" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB128" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC128" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD128" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE128" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF128" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG128" s="53" t="s">
         <v>917</v>
@@ -20533,25 +20514,25 @@
         <v>904</v>
       </c>
       <c r="Z129" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA129" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB129" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC129" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD129" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE129" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF129" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG129" s="53" t="s">
         <v>917</v>
@@ -20634,25 +20615,25 @@
         <v>904</v>
       </c>
       <c r="Z130" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA130" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB130" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC130" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD130" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE130" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF130" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG130" s="53" t="s">
         <v>917</v>
@@ -20735,25 +20716,25 @@
         <v>904</v>
       </c>
       <c r="Z131" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA131" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB131" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC131" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD131" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE131" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF131" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG131" s="53" t="s">
         <v>917</v>
@@ -20836,25 +20817,25 @@
         <v>904</v>
       </c>
       <c r="Z132" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA132" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB132" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC132" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD132" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE132" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF132" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG132" s="53" t="s">
         <v>917</v>
@@ -20937,25 +20918,25 @@
         <v>904</v>
       </c>
       <c r="Z133" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA133" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB133" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC133" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD133" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE133" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF133" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG133" s="53" t="s">
         <v>917</v>
@@ -21038,25 +21019,25 @@
         <v>904</v>
       </c>
       <c r="Z134" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA134" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB134" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC134" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD134" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE134" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF134" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG134" s="53" t="s">
         <v>917</v>
@@ -21139,25 +21120,25 @@
         <v>904</v>
       </c>
       <c r="Z135" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA135" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB135" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC135" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD135" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE135" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF135" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG135" s="53" t="s">
         <v>917</v>
@@ -21240,25 +21221,25 @@
         <v>904</v>
       </c>
       <c r="Z136" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA136" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB136" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC136" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD136" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE136" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF136" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG136" s="53" t="s">
         <v>917</v>
@@ -21341,25 +21322,25 @@
         <v>904</v>
       </c>
       <c r="Z137" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA137" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB137" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC137" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD137" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE137" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF137" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG137" s="53" t="s">
         <v>917</v>
@@ -21442,25 +21423,25 @@
         <v>904</v>
       </c>
       <c r="Z138" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA138" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB138" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC138" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD138" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE138" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF138" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG138" s="53" t="s">
         <v>917</v>
@@ -21543,25 +21524,25 @@
         <v>904</v>
       </c>
       <c r="Z139" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA139" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB139" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC139" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD139" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE139" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF139" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG139" s="53" t="s">
         <v>917</v>
@@ -21644,25 +21625,25 @@
         <v>904</v>
       </c>
       <c r="Z140" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA140" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB140" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC140" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD140" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE140" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF140" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG140" s="53" t="s">
         <v>917</v>
@@ -21745,25 +21726,25 @@
         <v>904</v>
       </c>
       <c r="Z141" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA141" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB141" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC141" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD141" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE141" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF141" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG141" s="53" t="s">
         <v>917</v>
@@ -21846,25 +21827,25 @@
         <v>904</v>
       </c>
       <c r="Z142" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA142" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB142" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC142" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD142" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE142" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF142" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG142" s="53" t="s">
         <v>917</v>
@@ -21947,25 +21928,25 @@
         <v>904</v>
       </c>
       <c r="Z143" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA143" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB143" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC143" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD143" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE143" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF143" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG143" s="53" t="s">
         <v>917</v>
@@ -22048,25 +22029,25 @@
         <v>904</v>
       </c>
       <c r="Z144" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA144" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB144" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC144" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD144" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE144" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF144" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG144" s="53" t="s">
         <v>917</v>
@@ -22149,25 +22130,25 @@
         <v>904</v>
       </c>
       <c r="Z145" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA145" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB145" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC145" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD145" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE145" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF145" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG145" s="53" t="s">
         <v>917</v>
@@ -22250,25 +22231,25 @@
         <v>904</v>
       </c>
       <c r="Z146" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA146" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB146" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC146" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD146" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE146" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF146" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG146" s="53" t="s">
         <v>917</v>
@@ -22351,25 +22332,25 @@
         <v>904</v>
       </c>
       <c r="Z147" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA147" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB147" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC147" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD147" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE147" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF147" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG147" s="53" t="s">
         <v>917</v>
@@ -22452,25 +22433,25 @@
         <v>904</v>
       </c>
       <c r="Z148" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA148" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB148" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC148" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD148" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE148" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF148" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG148" s="53" t="s">
         <v>917</v>
@@ -22553,25 +22534,25 @@
         <v>904</v>
       </c>
       <c r="Z149" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA149" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB149" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC149" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD149" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE149" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF149" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG149" s="53" t="s">
         <v>917</v>
@@ -22654,25 +22635,25 @@
         <v>904</v>
       </c>
       <c r="Z150" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA150" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB150" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC150" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD150" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE150" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF150" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG150" s="53" t="s">
         <v>917</v>
@@ -22755,25 +22736,25 @@
         <v>904</v>
       </c>
       <c r="Z151" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA151" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB151" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC151" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD151" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE151" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF151" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG151" s="53" t="s">
         <v>917</v>
@@ -22856,25 +22837,25 @@
         <v>904</v>
       </c>
       <c r="Z152" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA152" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB152" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC152" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD152" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE152" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF152" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG152" s="53" t="s">
         <v>917</v>
@@ -22957,25 +22938,25 @@
         <v>904</v>
       </c>
       <c r="Z153" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA153" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB153" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC153" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD153" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE153" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF153" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG153" s="53" t="s">
         <v>917</v>
@@ -23058,25 +23039,25 @@
         <v>904</v>
       </c>
       <c r="Z154" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA154" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB154" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC154" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD154" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE154" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF154" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG154" s="53" t="s">
         <v>917</v>
@@ -23159,25 +23140,25 @@
         <v>904</v>
       </c>
       <c r="Z155" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA155" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB155" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC155" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD155" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE155" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF155" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG155" s="53" t="s">
         <v>917</v>
@@ -23260,25 +23241,25 @@
         <v>904</v>
       </c>
       <c r="Z156" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA156" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB156" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC156" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD156" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE156" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF156" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG156" s="53" t="s">
         <v>917</v>
@@ -23361,25 +23342,25 @@
         <v>904</v>
       </c>
       <c r="Z157" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA157" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB157" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC157" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD157" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE157" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF157" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG157" s="53" t="s">
         <v>917</v>
@@ -23462,25 +23443,25 @@
         <v>904</v>
       </c>
       <c r="Z158" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA158" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB158" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC158" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD158" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE158" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF158" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG158" s="53" t="s">
         <v>917</v>
@@ -23563,25 +23544,25 @@
         <v>904</v>
       </c>
       <c r="Z159" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA159" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB159" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC159" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD159" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE159" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF159" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG159" s="53" t="s">
         <v>917</v>
@@ -23664,25 +23645,25 @@
         <v>904</v>
       </c>
       <c r="Z160" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA160" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB160" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC160" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD160" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE160" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF160" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG160" s="53" t="s">
         <v>917</v>
@@ -23765,25 +23746,25 @@
         <v>904</v>
       </c>
       <c r="Z161" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA161" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB161" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC161" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD161" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE161" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF161" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG161" s="53" t="s">
         <v>917</v>
@@ -23866,25 +23847,25 @@
         <v>904</v>
       </c>
       <c r="Z162" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA162" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB162" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC162" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD162" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE162" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF162" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG162" s="53" t="s">
         <v>917</v>
@@ -23967,25 +23948,25 @@
         <v>904</v>
       </c>
       <c r="Z163" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA163" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB163" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC163" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD163" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE163" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF163" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG163" s="53" t="s">
         <v>917</v>
@@ -24068,25 +24049,25 @@
         <v>904</v>
       </c>
       <c r="Z164" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA164" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB164" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC164" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD164" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE164" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF164" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG164" s="53" t="s">
         <v>917</v>
@@ -24169,25 +24150,25 @@
         <v>904</v>
       </c>
       <c r="Z165" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA165" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB165" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC165" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD165" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE165" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF165" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG165" s="53" t="s">
         <v>917</v>
@@ -24270,25 +24251,25 @@
         <v>904</v>
       </c>
       <c r="Z166" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA166" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB166" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC166" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD166" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE166" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF166" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG166" s="53" t="s">
         <v>917</v>
@@ -24371,25 +24352,25 @@
         <v>904</v>
       </c>
       <c r="Z167" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA167" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB167" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC167" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD167" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE167" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF167" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG167" s="53" t="s">
         <v>917</v>
@@ -24472,25 +24453,25 @@
         <v>904</v>
       </c>
       <c r="Z168" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA168" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB168" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC168" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD168" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE168" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF168" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG168" s="53" t="s">
         <v>917</v>
@@ -24573,25 +24554,25 @@
         <v>904</v>
       </c>
       <c r="Z169" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA169" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB169" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC169" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD169" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE169" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF169" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG169" s="53" t="s">
         <v>917</v>
@@ -24674,25 +24655,25 @@
         <v>904</v>
       </c>
       <c r="Z170" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA170" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB170" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC170" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD170" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE170" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF170" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG170" s="53" t="s">
         <v>917</v>
@@ -24775,25 +24756,25 @@
         <v>904</v>
       </c>
       <c r="Z171" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA171" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB171" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC171" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD171" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE171" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF171" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG171" s="53" t="s">
         <v>917</v>
@@ -24876,25 +24857,25 @@
         <v>904</v>
       </c>
       <c r="Z172" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA172" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB172" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC172" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD172" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE172" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF172" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG172" s="53" t="s">
         <v>917</v>
@@ -24977,25 +24958,25 @@
         <v>904</v>
       </c>
       <c r="Z173" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA173" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB173" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC173" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD173" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE173" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF173" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG173" s="53" t="s">
         <v>917</v>
@@ -25078,25 +25059,25 @@
         <v>904</v>
       </c>
       <c r="Z174" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA174" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB174" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC174" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD174" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE174" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF174" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG174" s="53" t="s">
         <v>917</v>
@@ -25179,25 +25160,25 @@
         <v>904</v>
       </c>
       <c r="Z175" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA175" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB175" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC175" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD175" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE175" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF175" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG175" s="53" t="s">
         <v>917</v>
@@ -25280,25 +25261,25 @@
         <v>904</v>
       </c>
       <c r="Z176" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA176" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB176" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC176" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD176" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE176" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF176" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG176" s="53" t="s">
         <v>917</v>
@@ -25381,25 +25362,25 @@
         <v>904</v>
       </c>
       <c r="Z177" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA177" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB177" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC177" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD177" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE177" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF177" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG177" s="53" t="s">
         <v>917</v>
@@ -25482,25 +25463,25 @@
         <v>904</v>
       </c>
       <c r="Z178" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA178" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB178" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC178" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD178" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE178" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF178" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG178" s="53" t="s">
         <v>917</v>
@@ -25583,25 +25564,25 @@
         <v>904</v>
       </c>
       <c r="Z179" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA179" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB179" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC179" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD179" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE179" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF179" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG179" s="53" t="s">
         <v>917</v>
@@ -25684,25 +25665,25 @@
         <v>904</v>
       </c>
       <c r="Z180" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA180" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB180" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC180" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD180" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE180" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF180" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG180" s="53" t="s">
         <v>917</v>
@@ -25785,25 +25766,25 @@
         <v>904</v>
       </c>
       <c r="Z181" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA181" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB181" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC181" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD181" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE181" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF181" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG181" s="53" t="s">
         <v>917</v>
@@ -25886,25 +25867,25 @@
         <v>904</v>
       </c>
       <c r="Z182" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA182" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB182" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC182" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD182" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE182" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF182" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG182" s="53" t="s">
         <v>917</v>
@@ -25987,25 +25968,25 @@
         <v>904</v>
       </c>
       <c r="Z183" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA183" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB183" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC183" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD183" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE183" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF183" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG183" s="53" t="s">
         <v>917</v>
@@ -26088,25 +26069,25 @@
         <v>904</v>
       </c>
       <c r="Z184" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA184" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB184" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC184" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD184" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE184" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF184" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG184" s="53" t="s">
         <v>917</v>
@@ -26189,25 +26170,25 @@
         <v>904</v>
       </c>
       <c r="Z185" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA185" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB185" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC185" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD185" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE185" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF185" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG185" s="53" t="s">
         <v>917</v>
@@ -26290,25 +26271,25 @@
         <v>904</v>
       </c>
       <c r="Z186" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA186" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB186" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC186" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD186" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE186" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF186" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG186" s="53" t="s">
         <v>917</v>
@@ -26391,25 +26372,25 @@
         <v>904</v>
       </c>
       <c r="Z187" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA187" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB187" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC187" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD187" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE187" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF187" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG187" s="53" t="s">
         <v>917</v>
@@ -26492,25 +26473,25 @@
         <v>904</v>
       </c>
       <c r="Z188" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA188" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB188" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC188" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD188" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE188" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF188" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG188" s="53" t="s">
         <v>917</v>
@@ -26593,25 +26574,25 @@
         <v>904</v>
       </c>
       <c r="Z189" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA189" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB189" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC189" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD189" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE189" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF189" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG189" s="53" t="s">
         <v>917</v>
@@ -26694,25 +26675,25 @@
         <v>904</v>
       </c>
       <c r="Z190" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA190" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB190" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC190" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD190" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE190" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF190" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG190" s="53" t="s">
         <v>917</v>
@@ -26795,25 +26776,25 @@
         <v>904</v>
       </c>
       <c r="Z191" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA191" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB191" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC191" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD191" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE191" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF191" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG191" s="53" t="s">
         <v>917</v>
@@ -26896,25 +26877,25 @@
         <v>904</v>
       </c>
       <c r="Z192" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA192" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB192" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC192" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD192" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE192" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF192" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG192" s="53" t="s">
         <v>917</v>
@@ -26997,25 +26978,25 @@
         <v>904</v>
       </c>
       <c r="Z193" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA193" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB193" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC193" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD193" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE193" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF193" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG193" s="53" t="s">
         <v>917</v>
@@ -27098,25 +27079,25 @@
         <v>904</v>
       </c>
       <c r="Z194" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA194" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB194" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC194" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD194" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE194" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF194" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG194" s="53" t="s">
         <v>917</v>
@@ -27199,25 +27180,25 @@
         <v>904</v>
       </c>
       <c r="Z195" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA195" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB195" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC195" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD195" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE195" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF195" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG195" s="53" t="s">
         <v>917</v>
@@ -27300,25 +27281,25 @@
         <v>904</v>
       </c>
       <c r="Z196" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA196" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB196" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC196" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD196" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE196" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF196" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG196" s="53" t="s">
         <v>917</v>
@@ -27401,25 +27382,25 @@
         <v>904</v>
       </c>
       <c r="Z197" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA197" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB197" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC197" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD197" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE197" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF197" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG197" s="53" t="s">
         <v>917</v>
@@ -27502,25 +27483,25 @@
         <v>904</v>
       </c>
       <c r="Z198" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA198" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB198" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC198" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD198" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE198" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF198" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG198" s="53" t="s">
         <v>917</v>
@@ -27603,25 +27584,25 @@
         <v>904</v>
       </c>
       <c r="Z199" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA199" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB199" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC199" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD199" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE199" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF199" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG199" s="53" t="s">
         <v>917</v>
@@ -27704,25 +27685,25 @@
         <v>904</v>
       </c>
       <c r="Z200" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA200" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB200" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC200" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD200" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE200" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF200" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG200" s="53" t="s">
         <v>917</v>
@@ -27805,25 +27786,25 @@
         <v>904</v>
       </c>
       <c r="Z201" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA201" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB201" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC201" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD201" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE201" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF201" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG201" s="53" t="s">
         <v>917</v>
@@ -27906,25 +27887,25 @@
         <v>904</v>
       </c>
       <c r="Z202" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA202" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB202" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC202" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD202" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE202" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF202" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG202" s="53" t="s">
         <v>917</v>
@@ -28007,25 +27988,25 @@
         <v>904</v>
       </c>
       <c r="Z203" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA203" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB203" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC203" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD203" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE203" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF203" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG203" s="53" t="s">
         <v>917</v>
@@ -28108,25 +28089,25 @@
         <v>904</v>
       </c>
       <c r="Z204" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA204" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB204" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC204" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD204" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE204" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF204" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG204" s="53" t="s">
         <v>917</v>
@@ -28209,25 +28190,25 @@
         <v>904</v>
       </c>
       <c r="Z205" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA205" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB205" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC205" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD205" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE205" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF205" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG205" s="53" t="s">
         <v>917</v>
@@ -28310,25 +28291,25 @@
         <v>904</v>
       </c>
       <c r="Z206" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA206" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB206" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC206" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD206" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE206" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF206" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG206" s="53" t="s">
         <v>917</v>
@@ -28411,25 +28392,25 @@
         <v>904</v>
       </c>
       <c r="Z207" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA207" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB207" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC207" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD207" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE207" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF207" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG207" s="53" t="s">
         <v>917</v>
@@ -28512,25 +28493,25 @@
         <v>904</v>
       </c>
       <c r="Z208" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA208" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB208" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC208" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD208" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE208" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF208" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG208" s="53" t="s">
         <v>917</v>
@@ -28613,25 +28594,25 @@
         <v>904</v>
       </c>
       <c r="Z209" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA209" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB209" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC209" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD209" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE209" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF209" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG209" s="53" t="s">
         <v>917</v>
@@ -28714,25 +28695,25 @@
         <v>904</v>
       </c>
       <c r="Z210" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA210" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB210" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC210" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD210" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE210" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF210" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG210" s="53" t="s">
         <v>917</v>
@@ -28815,25 +28796,25 @@
         <v>904</v>
       </c>
       <c r="Z211" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA211" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB211" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC211" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD211" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE211" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF211" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG211" s="53" t="s">
         <v>917</v>
@@ -28916,25 +28897,25 @@
         <v>904</v>
       </c>
       <c r="Z212" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA212" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB212" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC212" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD212" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE212" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF212" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG212" s="53" t="s">
         <v>917</v>
@@ -29017,25 +28998,25 @@
         <v>904</v>
       </c>
       <c r="Z213" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA213" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB213" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC213" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD213" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE213" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF213" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG213" s="53" t="s">
         <v>917</v>
@@ -29118,25 +29099,25 @@
         <v>904</v>
       </c>
       <c r="Z214" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA214" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB214" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC214" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD214" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE214" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF214" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG214" s="53" t="s">
         <v>917</v>
@@ -29219,25 +29200,25 @@
         <v>904</v>
       </c>
       <c r="Z215" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA215" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB215" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC215" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD215" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE215" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF215" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG215" s="53" t="s">
         <v>917</v>
@@ -29320,25 +29301,25 @@
         <v>904</v>
       </c>
       <c r="Z216" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA216" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB216" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC216" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD216" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE216" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF216" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG216" s="53" t="s">
         <v>917</v>
@@ -29421,25 +29402,25 @@
         <v>904</v>
       </c>
       <c r="Z217" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA217" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB217" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC217" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD217" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE217" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF217" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG217" s="53" t="s">
         <v>917</v>
@@ -29522,25 +29503,25 @@
         <v>904</v>
       </c>
       <c r="Z218" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA218" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB218" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC218" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD218" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE218" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF218" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG218" s="53" t="s">
         <v>917</v>
@@ -29623,25 +29604,25 @@
         <v>904</v>
       </c>
       <c r="Z219" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA219" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB219" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC219" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD219" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE219" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF219" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG219" s="53" t="s">
         <v>917</v>
@@ -29724,25 +29705,25 @@
         <v>904</v>
       </c>
       <c r="Z220" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA220" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB220" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC220" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD220" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE220" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF220" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG220" s="53" t="s">
         <v>917</v>
@@ -29825,25 +29806,25 @@
         <v>904</v>
       </c>
       <c r="Z221" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA221" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB221" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC221" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD221" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE221" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF221" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG221" s="53" t="s">
         <v>917</v>
@@ -29926,25 +29907,25 @@
         <v>904</v>
       </c>
       <c r="Z222" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA222" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB222" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC222" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD222" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE222" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF222" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG222" s="53" t="s">
         <v>917</v>
@@ -30027,25 +30008,25 @@
         <v>904</v>
       </c>
       <c r="Z223" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA223" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB223" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC223" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD223" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE223" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF223" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG223" s="53" t="s">
         <v>917</v>
@@ -30128,25 +30109,25 @@
         <v>904</v>
       </c>
       <c r="Z224" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA224" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB224" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC224" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD224" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE224" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF224" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG224" s="53" t="s">
         <v>917</v>
@@ -30229,25 +30210,25 @@
         <v>904</v>
       </c>
       <c r="Z225" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA225" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB225" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC225" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD225" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE225" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF225" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG225" s="53" t="s">
         <v>917</v>
@@ -30330,25 +30311,25 @@
         <v>904</v>
       </c>
       <c r="Z226" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA226" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB226" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC226" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD226" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE226" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF226" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG226" s="53" t="s">
         <v>917</v>
@@ -30431,25 +30412,25 @@
         <v>904</v>
       </c>
       <c r="Z227" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA227" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB227" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC227" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD227" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE227" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF227" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG227" s="53" t="s">
         <v>917</v>
@@ -30532,25 +30513,25 @@
         <v>904</v>
       </c>
       <c r="Z228" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA228" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB228" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC228" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD228" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE228" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF228" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG228" s="53" t="s">
         <v>917</v>
@@ -30633,25 +30614,25 @@
         <v>904</v>
       </c>
       <c r="Z229" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA229" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB229" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC229" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD229" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE229" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF229" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG229" s="53" t="s">
         <v>917</v>
@@ -30734,25 +30715,25 @@
         <v>904</v>
       </c>
       <c r="Z230" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA230" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB230" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC230" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD230" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE230" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF230" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG230" s="53" t="s">
         <v>917</v>
@@ -30835,25 +30816,25 @@
         <v>904</v>
       </c>
       <c r="Z231" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA231" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB231" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC231" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD231" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE231" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF231" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG231" s="53" t="s">
         <v>917</v>
@@ -30936,25 +30917,25 @@
         <v>904</v>
       </c>
       <c r="Z232" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA232" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB232" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC232" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD232" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE232" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF232" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG232" s="53" t="s">
         <v>917</v>
@@ -31037,25 +31018,25 @@
         <v>904</v>
       </c>
       <c r="Z233" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA233" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB233" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC233" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD233" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE233" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF233" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG233" s="53" t="s">
         <v>917</v>
@@ -31138,25 +31119,25 @@
         <v>904</v>
       </c>
       <c r="Z234" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA234" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB234" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC234" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD234" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE234" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF234" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG234" s="53" t="s">
         <v>917</v>
@@ -31239,25 +31220,25 @@
         <v>904</v>
       </c>
       <c r="Z235" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA235" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB235" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC235" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD235" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE235" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF235" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG235" s="53" t="s">
         <v>917</v>
@@ -31340,25 +31321,25 @@
         <v>904</v>
       </c>
       <c r="Z236" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA236" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB236" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC236" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD236" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE236" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF236" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG236" s="53" t="s">
         <v>917</v>
@@ -31441,25 +31422,25 @@
         <v>904</v>
       </c>
       <c r="Z237" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA237" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB237" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC237" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD237" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE237" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF237" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG237" s="53" t="s">
         <v>917</v>
@@ -31542,25 +31523,25 @@
         <v>904</v>
       </c>
       <c r="Z238" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA238" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB238" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC238" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD238" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE238" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF238" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG238" s="53" t="s">
         <v>917</v>
@@ -31643,25 +31624,25 @@
         <v>904</v>
       </c>
       <c r="Z239" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA239" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB239" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC239" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD239" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE239" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF239" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG239" s="53" t="s">
         <v>917</v>
@@ -31744,25 +31725,25 @@
         <v>904</v>
       </c>
       <c r="Z240" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA240" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB240" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC240" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD240" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE240" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF240" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG240" s="53" t="s">
         <v>917</v>
@@ -31845,25 +31826,25 @@
         <v>904</v>
       </c>
       <c r="Z241" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA241" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB241" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC241" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD241" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE241" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF241" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG241" s="53" t="s">
         <v>917</v>
@@ -31946,25 +31927,25 @@
         <v>904</v>
       </c>
       <c r="Z242" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA242" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB242" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC242" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD242" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE242" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF242" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG242" s="53" t="s">
         <v>917</v>
@@ -32047,25 +32028,25 @@
         <v>904</v>
       </c>
       <c r="Z243" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA243" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB243" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC243" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD243" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE243" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF243" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG243" s="53" t="s">
         <v>917</v>
@@ -32148,25 +32129,25 @@
         <v>904</v>
       </c>
       <c r="Z244" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA244" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB244" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC244" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD244" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE244" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF244" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG244" s="53" t="s">
         <v>917</v>
@@ -32249,25 +32230,25 @@
         <v>904</v>
       </c>
       <c r="Z245" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA245" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB245" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC245" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD245" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE245" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF245" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG245" s="53" t="s">
         <v>917</v>
@@ -32350,25 +32331,25 @@
         <v>904</v>
       </c>
       <c r="Z246" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA246" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB246" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC246" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD246" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE246" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF246" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG246" s="53" t="s">
         <v>917</v>
@@ -32451,25 +32432,25 @@
         <v>904</v>
       </c>
       <c r="Z247" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA247" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB247" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC247" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD247" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE247" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF247" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG247" s="53" t="s">
         <v>917</v>
@@ -32552,25 +32533,25 @@
         <v>904</v>
       </c>
       <c r="Z248" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA248" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB248" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC248" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD248" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE248" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF248" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG248" s="53" t="s">
         <v>917</v>
@@ -32653,25 +32634,25 @@
         <v>904</v>
       </c>
       <c r="Z249" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA249" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB249" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC249" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD249" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE249" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF249" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG249" s="53" t="s">
         <v>917</v>
@@ -32754,25 +32735,25 @@
         <v>904</v>
       </c>
       <c r="Z250" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA250" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB250" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC250" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD250" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE250" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF250" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG250" s="53" t="s">
         <v>917</v>
@@ -32855,25 +32836,25 @@
         <v>904</v>
       </c>
       <c r="Z251" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA251" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB251" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC251" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD251" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE251" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF251" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG251" s="53" t="s">
         <v>917</v>
@@ -32956,25 +32937,25 @@
         <v>904</v>
       </c>
       <c r="Z252" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA252" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB252" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC252" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD252" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE252" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF252" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG252" s="53" t="s">
         <v>917</v>
@@ -33057,25 +33038,25 @@
         <v>904</v>
       </c>
       <c r="Z253" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA253" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB253" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC253" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD253" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE253" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF253" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG253" s="53" t="s">
         <v>917</v>
@@ -33158,25 +33139,25 @@
         <v>904</v>
       </c>
       <c r="Z254" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA254" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB254" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC254" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD254" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE254" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF254" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG254" s="53" t="s">
         <v>917</v>
@@ -33259,25 +33240,25 @@
         <v>904</v>
       </c>
       <c r="Z255" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA255" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB255" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC255" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD255" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE255" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF255" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG255" s="53" t="s">
         <v>917</v>
@@ -33360,25 +33341,25 @@
         <v>904</v>
       </c>
       <c r="Z256" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA256" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB256" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC256" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD256" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE256" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF256" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG256" s="53" t="s">
         <v>917</v>
@@ -33461,25 +33442,25 @@
         <v>904</v>
       </c>
       <c r="Z257" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA257" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB257" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC257" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD257" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE257" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF257" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG257" s="53" t="s">
         <v>917</v>
@@ -33562,25 +33543,25 @@
         <v>904</v>
       </c>
       <c r="Z258" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA258" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB258" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC258" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD258" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE258" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF258" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG258" s="53" t="s">
         <v>917</v>
@@ -33663,25 +33644,25 @@
         <v>904</v>
       </c>
       <c r="Z259" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA259" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB259" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC259" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD259" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE259" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF259" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG259" s="53" t="s">
         <v>917</v>
@@ -33764,25 +33745,25 @@
         <v>904</v>
       </c>
       <c r="Z260" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA260" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB260" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC260" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD260" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE260" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF260" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG260" s="53" t="s">
         <v>917</v>
@@ -33865,25 +33846,25 @@
         <v>904</v>
       </c>
       <c r="Z261" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA261" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB261" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC261" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD261" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE261" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF261" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG261" s="53" t="s">
         <v>917</v>
@@ -33966,25 +33947,25 @@
         <v>904</v>
       </c>
       <c r="Z262" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA262" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB262" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC262" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD262" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE262" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF262" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG262" s="53" t="s">
         <v>917</v>
@@ -34067,25 +34048,25 @@
         <v>904</v>
       </c>
       <c r="Z263" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA263" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB263" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC263" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD263" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE263" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF263" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG263" s="53" t="s">
         <v>917</v>
@@ -34168,25 +34149,25 @@
         <v>904</v>
       </c>
       <c r="Z264" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA264" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB264" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC264" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD264" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE264" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF264" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG264" s="53" t="s">
         <v>917</v>
@@ -34269,25 +34250,25 @@
         <v>904</v>
       </c>
       <c r="Z265" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA265" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB265" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC265" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD265" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE265" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF265" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG265" s="53" t="s">
         <v>917</v>
@@ -34370,25 +34351,25 @@
         <v>904</v>
       </c>
       <c r="Z266" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA266" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB266" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC266" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD266" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE266" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF266" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG266" s="53" t="s">
         <v>917</v>
@@ -34471,25 +34452,25 @@
         <v>904</v>
       </c>
       <c r="Z267" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA267" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB267" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC267" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD267" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE267" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF267" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG267" s="53" t="s">
         <v>917</v>
@@ -34572,25 +34553,25 @@
         <v>904</v>
       </c>
       <c r="Z268" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA268" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB268" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC268" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD268" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE268" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF268" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG268" s="53" t="s">
         <v>917</v>
@@ -34673,25 +34654,25 @@
         <v>904</v>
       </c>
       <c r="Z269" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA269" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB269" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC269" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD269" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE269" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF269" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG269" s="53" t="s">
         <v>917</v>
@@ -34774,25 +34755,25 @@
         <v>904</v>
       </c>
       <c r="Z270" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA270" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB270" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC270" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD270" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE270" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF270" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG270" s="53" t="s">
         <v>917</v>
@@ -34875,25 +34856,25 @@
         <v>904</v>
       </c>
       <c r="Z271" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA271" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB271" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC271" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD271" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE271" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF271" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG271" s="53" t="s">
         <v>917</v>
@@ -34976,25 +34957,25 @@
         <v>904</v>
       </c>
       <c r="Z272" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA272" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB272" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC272" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD272" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE272" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF272" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG272" s="53" t="s">
         <v>917</v>
@@ -35077,25 +35058,25 @@
         <v>904</v>
       </c>
       <c r="Z273" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA273" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB273" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC273" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD273" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE273" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF273" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG273" s="53" t="s">
         <v>917</v>
@@ -35178,25 +35159,25 @@
         <v>904</v>
       </c>
       <c r="Z274" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA274" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB274" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC274" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD274" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE274" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF274" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG274" s="53" t="s">
         <v>917</v>
@@ -35279,25 +35260,25 @@
         <v>904</v>
       </c>
       <c r="Z275" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA275" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB275" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC275" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD275" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE275" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF275" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG275" s="53" t="s">
         <v>917</v>
@@ -35380,25 +35361,25 @@
         <v>904</v>
       </c>
       <c r="Z276" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA276" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB276" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC276" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD276" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE276" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF276" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG276" s="53" t="s">
         <v>917</v>
@@ -35481,25 +35462,25 @@
         <v>904</v>
       </c>
       <c r="Z277" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA277" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB277" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC277" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD277" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE277" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF277" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG277" s="53" t="s">
         <v>917</v>
@@ -35582,25 +35563,25 @@
         <v>904</v>
       </c>
       <c r="Z278" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA278" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB278" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC278" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD278" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE278" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF278" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG278" s="53" t="s">
         <v>917</v>
@@ -35683,25 +35664,25 @@
         <v>904</v>
       </c>
       <c r="Z279" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA279" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB279" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC279" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD279" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE279" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF279" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG279" s="53" t="s">
         <v>917</v>
@@ -35784,25 +35765,25 @@
         <v>904</v>
       </c>
       <c r="Z280" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA280" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB280" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC280" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD280" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE280" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF280" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG280" s="53" t="s">
         <v>917</v>
@@ -35885,25 +35866,25 @@
         <v>904</v>
       </c>
       <c r="Z281" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA281" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB281" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC281" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD281" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE281" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF281" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG281" s="53" t="s">
         <v>917</v>
@@ -35986,25 +35967,25 @@
         <v>904</v>
       </c>
       <c r="Z282" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA282" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB282" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC282" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD282" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE282" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF282" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG282" s="53" t="s">
         <v>917</v>
@@ -36087,25 +36068,25 @@
         <v>904</v>
       </c>
       <c r="Z283" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA283" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB283" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC283" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD283" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE283" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF283" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG283" s="53" t="s">
         <v>917</v>
@@ -36188,25 +36169,25 @@
         <v>904</v>
       </c>
       <c r="Z284" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA284" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB284" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC284" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD284" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE284" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF284" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG284" s="53" t="s">
         <v>917</v>
@@ -36289,25 +36270,25 @@
         <v>904</v>
       </c>
       <c r="Z285" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA285" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB285" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC285" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD285" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE285" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF285" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG285" s="53" t="s">
         <v>917</v>
@@ -36390,25 +36371,25 @@
         <v>904</v>
       </c>
       <c r="Z286" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA286" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB286" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC286" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD286" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE286" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF286" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG286" s="53" t="s">
         <v>917</v>
@@ -36491,25 +36472,25 @@
         <v>904</v>
       </c>
       <c r="Z287" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA287" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB287" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC287" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD287" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE287" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF287" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG287" s="53" t="s">
         <v>917</v>
@@ -36592,25 +36573,25 @@
         <v>904</v>
       </c>
       <c r="Z288" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA288" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB288" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC288" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD288" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE288" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF288" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG288" s="53" t="s">
         <v>917</v>
@@ -36693,25 +36674,25 @@
         <v>904</v>
       </c>
       <c r="Z289" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA289" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB289" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC289" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD289" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE289" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF289" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG289" s="53" t="s">
         <v>917</v>
@@ -36794,25 +36775,25 @@
         <v>904</v>
       </c>
       <c r="Z290" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA290" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB290" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC290" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD290" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE290" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF290" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG290" s="53" t="s">
         <v>917</v>
@@ -36895,25 +36876,25 @@
         <v>904</v>
       </c>
       <c r="Z291" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA291" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB291" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC291" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD291" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE291" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF291" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG291" s="53" t="s">
         <v>917</v>
@@ -36996,25 +36977,25 @@
         <v>904</v>
       </c>
       <c r="Z292" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA292" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB292" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC292" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD292" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE292" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF292" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG292" s="53" t="s">
         <v>917</v>
@@ -37097,25 +37078,25 @@
         <v>904</v>
       </c>
       <c r="Z293" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA293" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB293" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC293" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD293" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE293" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF293" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG293" s="53" t="s">
         <v>917</v>
@@ -37198,25 +37179,25 @@
         <v>904</v>
       </c>
       <c r="Z294" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA294" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB294" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC294" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD294" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE294" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF294" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG294" s="53" t="s">
         <v>917</v>
@@ -37299,25 +37280,25 @@
         <v>904</v>
       </c>
       <c r="Z295" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA295" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB295" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC295" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD295" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE295" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF295" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG295" s="53" t="s">
         <v>917</v>
@@ -37400,25 +37381,25 @@
         <v>904</v>
       </c>
       <c r="Z296" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA296" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB296" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC296" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD296" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE296" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF296" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG296" s="53" t="s">
         <v>917</v>
@@ -37501,25 +37482,25 @@
         <v>904</v>
       </c>
       <c r="Z297" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA297" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB297" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC297" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD297" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE297" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF297" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG297" s="53" t="s">
         <v>917</v>
@@ -37602,25 +37583,25 @@
         <v>904</v>
       </c>
       <c r="Z298" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA298" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB298" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC298" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD298" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE298" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF298" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG298" s="53" t="s">
         <v>917</v>
@@ -37703,25 +37684,25 @@
         <v>904</v>
       </c>
       <c r="Z299" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA299" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB299" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC299" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD299" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE299" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF299" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG299" s="53" t="s">
         <v>917</v>
@@ -37804,25 +37785,25 @@
         <v>904</v>
       </c>
       <c r="Z300" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA300" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB300" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC300" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD300" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE300" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF300" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG300" s="53" t="s">
         <v>917</v>
@@ -37905,25 +37886,25 @@
         <v>904</v>
       </c>
       <c r="Z301" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA301" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB301" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC301" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD301" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE301" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF301" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG301" s="53" t="s">
         <v>917</v>
@@ -38006,25 +37987,25 @@
         <v>904</v>
       </c>
       <c r="Z302" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA302" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB302" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC302" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD302" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE302" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF302" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG302" s="53" t="s">
         <v>917</v>
@@ -38107,25 +38088,25 @@
         <v>904</v>
       </c>
       <c r="Z303" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA303" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB303" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC303" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD303" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE303" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF303" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG303" s="53" t="s">
         <v>917</v>
@@ -38208,25 +38189,25 @@
         <v>904</v>
       </c>
       <c r="Z304" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA304" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB304" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC304" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD304" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE304" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF304" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG304" s="53" t="s">
         <v>917</v>
@@ -38309,25 +38290,25 @@
         <v>904</v>
       </c>
       <c r="Z305" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA305" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB305" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC305" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD305" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE305" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF305" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG305" s="53" t="s">
         <v>917</v>
@@ -38379,11 +38360,12 @@
       <c r="O306" s="33" t="s">
         <v>907</v>
       </c>
-      <c r="P306" s="41" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q306" s="33" t="s">
-        <v>321</v>
+      <c r="P306" s="68" t="str">
+        <f t="shared" ref="P306:P310" si="0">IF(Q306="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="Q306" s="69" t="s">
+        <v>921</v>
       </c>
       <c r="R306" s="41" t="s">
         <v>321</v>
@@ -38410,25 +38392,25 @@
         <v>904</v>
       </c>
       <c r="Z306" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA306" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB306" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC306" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD306" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE306" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF306" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG306" s="53" t="s">
         <v>917</v>
@@ -38480,11 +38462,12 @@
       <c r="O307" s="33" t="s">
         <v>910</v>
       </c>
-      <c r="P307" s="41" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q307" s="33" t="s">
-        <v>321</v>
+      <c r="P307" s="68" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q307" s="69" t="s">
+        <v>922</v>
       </c>
       <c r="R307" s="41" t="s">
         <v>321</v>
@@ -38511,25 +38494,25 @@
         <v>904</v>
       </c>
       <c r="Z307" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA307" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB307" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC307" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD307" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE307" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF307" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG307" s="53" t="s">
         <v>917</v>
@@ -38581,11 +38564,12 @@
       <c r="O308" s="33" t="s">
         <v>913</v>
       </c>
-      <c r="P308" s="41" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q308" s="33" t="s">
-        <v>321</v>
+      <c r="P308" s="68" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q308" s="69" t="s">
+        <v>923</v>
       </c>
       <c r="R308" s="41" t="s">
         <v>321</v>
@@ -38612,25 +38596,25 @@
         <v>904</v>
       </c>
       <c r="Z308" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA308" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB308" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC308" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD308" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE308" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF308" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG308" s="53" t="s">
         <v>917</v>
@@ -38682,11 +38666,12 @@
       <c r="O309" s="33" t="s">
         <v>916</v>
       </c>
-      <c r="P309" s="41" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q309" s="33" t="s">
-        <v>321</v>
+      <c r="P309" s="68" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q309" s="69" t="s">
+        <v>924</v>
       </c>
       <c r="R309" s="41" t="s">
         <v>321</v>
@@ -38713,25 +38698,25 @@
         <v>904</v>
       </c>
       <c r="Z309" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA309" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB309" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC309" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD309" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE309" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF309" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG309" s="53" t="s">
         <v>917</v>
@@ -38783,11 +38768,12 @@
       <c r="O310" s="33" t="s">
         <v>919</v>
       </c>
-      <c r="P310" s="41" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q310" s="33" t="s">
-        <v>321</v>
+      <c r="P310" s="68" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q310" s="69" t="s">
+        <v>925</v>
       </c>
       <c r="R310" s="41" t="s">
         <v>321</v>
@@ -38814,25 +38800,25 @@
         <v>904</v>
       </c>
       <c r="Z310" s="52" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AA310" s="53" t="s">
         <v>908</v>
       </c>
       <c r="AB310" s="52" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="AC310" s="53" t="s">
         <v>911</v>
       </c>
       <c r="AD310" s="52" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AE310" s="53" t="s">
         <v>914</v>
       </c>
       <c r="AF310" s="52" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="AG310" s="53" t="s">
         <v>917</v>
@@ -38841,118 +38827,93 @@
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="B1:B305 B311:B1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B306:B310">
-    <cfRule type="duplicateValues" dxfId="23" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="21" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="20" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="28" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="19" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="27" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="17" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="16" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P306:W310">
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
+  <conditionalFormatting sqref="R306:W310">
+    <cfRule type="cellIs" dxfId="10" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T1:AG1 T2:W305 T311:Y1048576">
-    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
+  <conditionalFormatting sqref="T1:AG1 T2:W305 T311:Z1048576 AB311:AB1048576 AD311:AD1048576 AF311:AF1048576">
+    <cfRule type="cellIs" dxfId="7" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="11" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="22" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="21" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:AG310">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z4:AG310">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y310">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:AA3">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AC3">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AE3">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AG3">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>

--- a/Versão5/ABNT/Ontologia_NBR15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1S.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7A4BC5-B3A7-4D5F-8BB7-8067A0163412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914CD8DD-CBD7-42B6-A864-8C1B11C3ECEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -2856,19 +2856,19 @@
     <t>é.selecionado.por</t>
   </si>
   <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(SpatialElement)).Cast&lt;SpatialElement&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ FilteredElementCollector(doc).OfClass(typeof(Level)).Cast&lt;Level&gt;().OrderBy(e =&gt; e.Name).ToList() ]"</t>
-  </si>
-  <si>
-    <t>"[ EleBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilyInstance)).Cast&lt;FamilyInstance&gt;().FirstOrDefault( e =&gt; e.Symbol.Name == 'InsBuscada') ]"</t>
-  </si>
-  <si>
-    <t>"[ TipBuscado : FilteredElementCollector(doc).OfClass(typeof(FamilySymbol )).Cast&lt;FamilySymbol&gt;( ).FirstOrDefault( e =&gt; e.Name        == 'TipBuscado') ]"</t>
-  </si>
-  <si>
-    <t>"[ MtlBuscado : FilteredElementCollector(doc).OfClass(typeof(Material)).Cast&lt;Material&gt;( ).FirstOrDefault( e =&gt; e.Name  == 'MtlBuscado') ]"</t>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
   </si>
 </sst>
 </file>
@@ -3523,7 +3523,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -3531,7 +3531,7 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0"/>
       </font>
     </dxf>
     <dxf>
@@ -4048,14 +4048,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CFA2BD-3953-447B-BF8D-35BA528839AD}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>307</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>308</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="36" t="s">
         <v>9</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>309</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>311</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>312</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>313</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>314</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>315</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>316</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -4244,19 +4244,19 @@
         <v>689</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>317</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46257.755616435184</v>
+        <v>46258.544145138891</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>698</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="36" t="s">
         <v>692</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="36" t="s">
         <v>699</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>306</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>318</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>324</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>326</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="36" t="s">
         <v>685</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="36" t="s">
         <v>827</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="36" t="s">
         <v>829</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="36" t="s">
         <v>831</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="36" t="s">
         <v>833</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="36" t="s">
         <v>835</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="36" t="s">
         <v>837</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="36" t="s">
         <v>839</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="36" t="s">
         <v>841</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="36" t="s">
         <v>843</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="36" t="s">
         <v>845</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="36" t="s">
         <v>847</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>849</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="62" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="62" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="36" t="s">
         <v>851</v>
       </c>
@@ -4505,36 +4505,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6EEAB6-D26C-4450-83AD-F740CF51FA1E}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC28"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.296875" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.19921875" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" style="27" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.69921875" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.19921875" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" style="27" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="71.69921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="71.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="5" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.796875" style="27" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="45.19921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="45.1640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="44.796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="8" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>637</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="46">
         <v>2</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="46">
         <v>3</v>
       </c>
@@ -4817,7 +4817,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="46">
         <v>4</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46">
         <v>5</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="46">
         <v>6</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="46">
         <v>7</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="46">
         <v>8</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="46">
         <v>9</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="46">
         <v>10</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="46">
         <v>11</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="46">
         <v>12</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="46">
         <v>13</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="46">
         <v>14</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="46">
         <v>15</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="46">
         <v>16</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="46">
         <v>17</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="46">
         <v>18</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="46">
         <v>19</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="46">
         <v>20</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="46">
         <v>21</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="46">
         <v>22</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="46">
         <v>23</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="46">
         <v>24</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="46">
         <v>25</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="46">
         <v>26</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="46">
         <v>27</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="32" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" s="32" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="46">
         <v>28</v>
       </c>
@@ -7281,13 +7281,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEF6990-269C-482F-AEAB-0F771E87FB19}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>657</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -7434,13 +7434,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56C5A03-15CD-4694-84A2-E149E46D665B}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.796875" customWidth="1"/>
+    <col min="2" max="3" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -7476,44 +7476,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2864B2AC-DDFD-480C-BEC0-F2615FD9637A}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG310"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.09765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.3984375" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.33203125" style="32" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="80.59765625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.09765625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.09765625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.09765625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.69921875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.796875" customWidth="1"/>
-    <col min="25" max="25" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.796875" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.83203125" customWidth="1"/>
+    <col min="25" max="25" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.83203125" customWidth="1"/>
     <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.796875" customWidth="1"/>
+    <col min="28" max="28" width="10.83203125" customWidth="1"/>
     <col min="29" max="29" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.796875" customWidth="1"/>
-    <col min="31" max="31" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.796875" customWidth="1"/>
-    <col min="33" max="33" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.83203125" customWidth="1"/>
+    <col min="31" max="31" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.83203125" customWidth="1"/>
+    <col min="33" max="33" width="7.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>319</v>
       </c>
@@ -7610,7 +7610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -8519,7 +8519,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -9529,7 +9529,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -9731,7 +9731,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -10236,7 +10236,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -10337,7 +10337,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -10640,7 +10640,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -10741,7 +10741,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -11044,7 +11044,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -11246,7 +11246,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -11549,7 +11549,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -11650,7 +11650,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -11751,7 +11751,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -12054,7 +12054,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -12256,7 +12256,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -12357,7 +12357,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -12458,7 +12458,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -12559,7 +12559,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -12660,7 +12660,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -12761,7 +12761,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -12963,7 +12963,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -13064,7 +13064,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -13367,7 +13367,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -13468,7 +13468,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -13670,7 +13670,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -13771,7 +13771,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -13872,7 +13872,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -13973,7 +13973,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -14074,7 +14074,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -14175,7 +14175,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -14276,7 +14276,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -14478,7 +14478,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -14579,7 +14579,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -14680,7 +14680,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -14781,7 +14781,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -14882,7 +14882,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -14983,7 +14983,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -15084,7 +15084,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -15185,7 +15185,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -15286,7 +15286,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -15488,7 +15488,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -15589,7 +15589,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -15690,7 +15690,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -15791,7 +15791,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -16094,7 +16094,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -16195,7 +16195,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -16397,7 +16397,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -16498,7 +16498,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -16599,7 +16599,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -16700,7 +16700,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -16801,7 +16801,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -16902,7 +16902,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -17003,7 +17003,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -17104,7 +17104,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -17205,7 +17205,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -17306,7 +17306,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -17407,7 +17407,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -17508,7 +17508,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -17609,7 +17609,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -17710,7 +17710,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -17912,7 +17912,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -18013,7 +18013,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -18114,7 +18114,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -18215,7 +18215,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -18316,7 +18316,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -18518,7 +18518,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -18619,7 +18619,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -18720,7 +18720,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -18821,7 +18821,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -18922,7 +18922,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -19023,7 +19023,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -19124,7 +19124,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -19225,7 +19225,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -19326,7 +19326,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -19427,7 +19427,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -19528,7 +19528,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -19629,7 +19629,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -19730,7 +19730,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -19831,7 +19831,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -19932,7 +19932,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -20033,7 +20033,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -20134,7 +20134,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -20235,7 +20235,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -20336,7 +20336,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -20437,7 +20437,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -20538,7 +20538,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -20639,7 +20639,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -20740,7 +20740,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -20841,7 +20841,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -20942,7 +20942,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -21043,7 +21043,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -21245,7 +21245,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -21346,7 +21346,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -21447,7 +21447,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -21548,7 +21548,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -21649,7 +21649,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -21750,7 +21750,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -21851,7 +21851,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -21952,7 +21952,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -22053,7 +22053,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -22154,7 +22154,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -22255,7 +22255,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -22356,7 +22356,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -22457,7 +22457,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -22558,7 +22558,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -22659,7 +22659,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -22760,7 +22760,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -22861,7 +22861,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -22962,7 +22962,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -23063,7 +23063,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -23164,7 +23164,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="9">
         <v>157</v>
       </c>
@@ -23366,7 +23366,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="9">
         <v>158</v>
       </c>
@@ -23467,7 +23467,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="9">
         <v>159</v>
       </c>
@@ -23568,7 +23568,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="9">
         <v>160</v>
       </c>
@@ -23669,7 +23669,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="9">
         <v>161</v>
       </c>
@@ -23770,7 +23770,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="9">
         <v>162</v>
       </c>
@@ -23871,7 +23871,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="9">
         <v>163</v>
       </c>
@@ -23972,7 +23972,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="9">
         <v>164</v>
       </c>
@@ -24073,7 +24073,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="9">
         <v>165</v>
       </c>
@@ -24174,7 +24174,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="9">
         <v>166</v>
       </c>
@@ -24275,7 +24275,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="9">
         <v>167</v>
       </c>
@@ -24376,7 +24376,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="9">
         <v>168</v>
       </c>
@@ -24477,7 +24477,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="9">
         <v>169</v>
       </c>
@@ -24578,7 +24578,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="9">
         <v>170</v>
       </c>
@@ -24679,7 +24679,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="9">
         <v>171</v>
       </c>
@@ -24780,7 +24780,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="9">
         <v>172</v>
       </c>
@@ -24881,7 +24881,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="9">
         <v>173</v>
       </c>
@@ -24982,7 +24982,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="9">
         <v>174</v>
       </c>
@@ -25083,7 +25083,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="9">
         <v>175</v>
       </c>
@@ -25184,7 +25184,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="9">
         <v>176</v>
       </c>
@@ -25285,7 +25285,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="9">
         <v>177</v>
       </c>
@@ -25386,7 +25386,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="9">
         <v>178</v>
       </c>
@@ -25487,7 +25487,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="179" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="9">
         <v>179</v>
       </c>
@@ -25588,7 +25588,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="180" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="9">
         <v>180</v>
       </c>
@@ -25689,7 +25689,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="181" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="9">
         <v>181</v>
       </c>
@@ -25790,7 +25790,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="182" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="9">
         <v>182</v>
       </c>
@@ -25891,7 +25891,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="183" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="9">
         <v>183</v>
       </c>
@@ -25992,7 +25992,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="9">
         <v>184</v>
       </c>
@@ -26093,7 +26093,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="185" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="9">
         <v>185</v>
       </c>
@@ -26194,7 +26194,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="9">
         <v>186</v>
       </c>
@@ -26295,7 +26295,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="9">
         <v>187</v>
       </c>
@@ -26396,7 +26396,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="188" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="9">
         <v>188</v>
       </c>
@@ -26497,7 +26497,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="189" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="9">
         <v>189</v>
       </c>
@@ -26598,7 +26598,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="190" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="9">
         <v>190</v>
       </c>
@@ -26699,7 +26699,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="191" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="9">
         <v>191</v>
       </c>
@@ -26800,7 +26800,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="192" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="9">
         <v>192</v>
       </c>
@@ -26901,7 +26901,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="193" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="9">
         <v>193</v>
       </c>
@@ -27002,7 +27002,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="194" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="9">
         <v>194</v>
       </c>
@@ -27103,7 +27103,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="195" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="9">
         <v>195</v>
       </c>
@@ -27204,7 +27204,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="196" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="9">
         <v>196</v>
       </c>
@@ -27305,7 +27305,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="197" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="9">
         <v>197</v>
       </c>
@@ -27406,7 +27406,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="198" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="9">
         <v>198</v>
       </c>
@@ -27507,7 +27507,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="199" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="9">
         <v>199</v>
       </c>
@@ -27608,7 +27608,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="200" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="9">
         <v>200</v>
       </c>
@@ -27709,7 +27709,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="201" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="9">
         <v>201</v>
       </c>
@@ -27810,7 +27810,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="202" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="9">
         <v>202</v>
       </c>
@@ -27911,7 +27911,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="203" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="9">
         <v>203</v>
       </c>
@@ -28012,7 +28012,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="204" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="9">
         <v>204</v>
       </c>
@@ -28113,7 +28113,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="205" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="9">
         <v>205</v>
       </c>
@@ -28214,7 +28214,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="206" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="9">
         <v>206</v>
       </c>
@@ -28315,7 +28315,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="207" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="9">
         <v>207</v>
       </c>
@@ -28416,7 +28416,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="208" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="9">
         <v>208</v>
       </c>
@@ -28517,7 +28517,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="209" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="9">
         <v>209</v>
       </c>
@@ -28618,7 +28618,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="210" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="9">
         <v>210</v>
       </c>
@@ -28719,7 +28719,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="211" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="9">
         <v>211</v>
       </c>
@@ -28820,7 +28820,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="212" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="9">
         <v>212</v>
       </c>
@@ -28921,7 +28921,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="213" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="9">
         <v>213</v>
       </c>
@@ -29022,7 +29022,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="214" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="9">
         <v>214</v>
       </c>
@@ -29123,7 +29123,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="215" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="9">
         <v>215</v>
       </c>
@@ -29224,7 +29224,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="216" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="9">
         <v>216</v>
       </c>
@@ -29325,7 +29325,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="217" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="9">
         <v>217</v>
       </c>
@@ -29426,7 +29426,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="218" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="9">
         <v>218</v>
       </c>
@@ -29527,7 +29527,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="219" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="9">
         <v>219</v>
       </c>
@@ -29628,7 +29628,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="220" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="9">
         <v>220</v>
       </c>
@@ -29729,7 +29729,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="221" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="9">
         <v>221</v>
       </c>
@@ -29830,7 +29830,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="222" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="9">
         <v>222</v>
       </c>
@@ -29931,7 +29931,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="223" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="9">
         <v>223</v>
       </c>
@@ -30032,7 +30032,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="224" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="9">
         <v>224</v>
       </c>
@@ -30133,7 +30133,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="225" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="9">
         <v>225</v>
       </c>
@@ -30234,7 +30234,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="226" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="9">
         <v>226</v>
       </c>
@@ -30335,7 +30335,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="227" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="9">
         <v>227</v>
       </c>
@@ -30436,7 +30436,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="228" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="9">
         <v>228</v>
       </c>
@@ -30537,7 +30537,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="229" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="9">
         <v>229</v>
       </c>
@@ -30638,7 +30638,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="230" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="9">
         <v>230</v>
       </c>
@@ -30739,7 +30739,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="231" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="9">
         <v>231</v>
       </c>
@@ -30840,7 +30840,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="232" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="9">
         <v>232</v>
       </c>
@@ -30941,7 +30941,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="233" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="9">
         <v>233</v>
       </c>
@@ -31042,7 +31042,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="234" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="9">
         <v>234</v>
       </c>
@@ -31143,7 +31143,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="235" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="9">
         <v>235</v>
       </c>
@@ -31244,7 +31244,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="236" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="9">
         <v>236</v>
       </c>
@@ -31345,7 +31345,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="237" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="9">
         <v>237</v>
       </c>
@@ -31446,7 +31446,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="238" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="9">
         <v>238</v>
       </c>
@@ -31547,7 +31547,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="239" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="9">
         <v>239</v>
       </c>
@@ -31648,7 +31648,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="240" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="9">
         <v>240</v>
       </c>
@@ -31749,7 +31749,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="241" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="9">
         <v>241</v>
       </c>
@@ -31850,7 +31850,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="242" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="9">
         <v>242</v>
       </c>
@@ -31951,7 +31951,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="243" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="9">
         <v>243</v>
       </c>
@@ -32052,7 +32052,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="244" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="9">
         <v>244</v>
       </c>
@@ -32153,7 +32153,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="245" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="9">
         <v>245</v>
       </c>
@@ -32254,7 +32254,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="246" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="9">
         <v>246</v>
       </c>
@@ -32355,7 +32355,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="247" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="9">
         <v>247</v>
       </c>
@@ -32456,7 +32456,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="9">
         <v>248</v>
       </c>
@@ -32557,7 +32557,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="249" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="9">
         <v>249</v>
       </c>
@@ -32658,7 +32658,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="250" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="9">
         <v>250</v>
       </c>
@@ -32759,7 +32759,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="251" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="9">
         <v>251</v>
       </c>
@@ -32860,7 +32860,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="252" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="9">
         <v>252</v>
       </c>
@@ -32961,7 +32961,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="9">
         <v>253</v>
       </c>
@@ -33062,7 +33062,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="254" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="9">
         <v>254</v>
       </c>
@@ -33163,7 +33163,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="255" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="9">
         <v>255</v>
       </c>
@@ -33264,7 +33264,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="256" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="9">
         <v>256</v>
       </c>
@@ -33365,7 +33365,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="257" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="9">
         <v>257</v>
       </c>
@@ -33466,7 +33466,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="258" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="9">
         <v>258</v>
       </c>
@@ -33567,7 +33567,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="259" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="9">
         <v>259</v>
       </c>
@@ -33668,7 +33668,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="260" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="9">
         <v>260</v>
       </c>
@@ -33769,7 +33769,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="261" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="9">
         <v>261</v>
       </c>
@@ -33870,7 +33870,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="262" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="9">
         <v>262</v>
       </c>
@@ -33971,7 +33971,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="263" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="9">
         <v>263</v>
       </c>
@@ -34072,7 +34072,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="264" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="9">
         <v>264</v>
       </c>
@@ -34173,7 +34173,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="265" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="9">
         <v>265</v>
       </c>
@@ -34274,7 +34274,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="266" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="9">
         <v>266</v>
       </c>
@@ -34375,7 +34375,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="267" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="9">
         <v>267</v>
       </c>
@@ -34476,7 +34476,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="268" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="9">
         <v>268</v>
       </c>
@@ -34577,7 +34577,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="269" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="9">
         <v>269</v>
       </c>
@@ -34678,7 +34678,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="270" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="9">
         <v>270</v>
       </c>
@@ -34779,7 +34779,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="271" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="9">
         <v>271</v>
       </c>
@@ -34880,7 +34880,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="272" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="9">
         <v>272</v>
       </c>
@@ -34981,7 +34981,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="273" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="9">
         <v>273</v>
       </c>
@@ -35082,7 +35082,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="274" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="9">
         <v>274</v>
       </c>
@@ -35183,7 +35183,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="275" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="9">
         <v>275</v>
       </c>
@@ -35284,7 +35284,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="276" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="9">
         <v>276</v>
       </c>
@@ -35385,7 +35385,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="277" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="9">
         <v>277</v>
       </c>
@@ -35486,7 +35486,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="278" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="9">
         <v>278</v>
       </c>
@@ -35587,7 +35587,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="279" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="9">
         <v>279</v>
       </c>
@@ -35688,7 +35688,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="280" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="9">
         <v>280</v>
       </c>
@@ -35789,7 +35789,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="281" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="9">
         <v>281</v>
       </c>
@@ -35890,7 +35890,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="282" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="9">
         <v>282</v>
       </c>
@@ -35991,7 +35991,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="283" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="9">
         <v>283</v>
       </c>
@@ -36092,7 +36092,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="284" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="9">
         <v>284</v>
       </c>
@@ -36193,7 +36193,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="285" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="9">
         <v>285</v>
       </c>
@@ -36294,7 +36294,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="286" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="9">
         <v>286</v>
       </c>
@@ -36395,7 +36395,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="287" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="9">
         <v>287</v>
       </c>
@@ -36496,7 +36496,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="288" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="9">
         <v>288</v>
       </c>
@@ -36597,7 +36597,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="289" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="9">
         <v>289</v>
       </c>
@@ -36698,7 +36698,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="290" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="9">
         <v>290</v>
       </c>
@@ -36799,7 +36799,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="291" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="9">
         <v>291</v>
       </c>
@@ -36900,7 +36900,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="292" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="9">
         <v>292</v>
       </c>
@@ -37001,7 +37001,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="293" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="9">
         <v>293</v>
       </c>
@@ -37102,7 +37102,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="294" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="9">
         <v>294</v>
       </c>
@@ -37203,7 +37203,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="295" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="9">
         <v>295</v>
       </c>
@@ -37304,7 +37304,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="296" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="9">
         <v>296</v>
       </c>
@@ -37405,7 +37405,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="297" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="9">
         <v>297</v>
       </c>
@@ -37506,7 +37506,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="298" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="9">
         <v>298</v>
       </c>
@@ -37607,7 +37607,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="299" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="9">
         <v>299</v>
       </c>
@@ -37708,7 +37708,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="300" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="9">
         <v>300</v>
       </c>
@@ -37809,7 +37809,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="301" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="9">
         <v>301</v>
       </c>
@@ -37910,7 +37910,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="302" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="9">
         <v>302</v>
       </c>
@@ -38011,7 +38011,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="303" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="9">
         <v>303</v>
       </c>
@@ -38112,7 +38112,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="304" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="9">
         <v>304</v>
       </c>
@@ -38213,7 +38213,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="305" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="9">
         <v>305</v>
       </c>
@@ -38314,7 +38314,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="306" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="9">
         <v>306</v>
       </c>
@@ -38416,7 +38416,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="307" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="9">
         <v>307</v>
       </c>
@@ -38518,7 +38518,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="308" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="9">
         <v>308</v>
       </c>
@@ -38620,7 +38620,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="309" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="9">
         <v>309</v>
       </c>
@@ -38722,7 +38722,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="310" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="9">
         <v>310</v>
       </c>
@@ -38863,13 +38863,13 @@
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R306:W310">
-    <cfRule type="cellIs" dxfId="10" priority="15" operator="equal">
+  <conditionalFormatting sqref="R1">
+    <cfRule type="cellIs" dxfId="10" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="9" priority="24" operator="equal">
+  <conditionalFormatting sqref="R306:W310">
+    <cfRule type="cellIs" dxfId="9" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_NBR15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_NBR15965_1S.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914CD8DD-CBD7-42B6-A864-8C1B11C3ECEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A256EF7-9867-4518-BF1A-CB6555B48CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -4048,14 +4048,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CFA2BD-3953-447B-BF8D-35BA528839AD}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>307</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>308</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -4099,7 +4099,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="36" t="s">
         <v>9</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>309</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>311</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>312</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>313</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>314</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>315</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>316</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -4244,19 +4244,19 @@
         <v>689</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>317</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46258.544145138891</v>
+        <v>46264.561511458334</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>698</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="36" t="s">
         <v>692</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="36" t="s">
         <v>699</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>306</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>318</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>324</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>326</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="36" t="s">
         <v>685</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="36" t="s">
         <v>827</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="36" t="s">
         <v>829</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="36" t="s">
         <v>831</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="36" t="s">
         <v>833</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="36" t="s">
         <v>835</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="36" t="s">
         <v>837</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="36" t="s">
         <v>839</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="36" t="s">
         <v>841</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="36" t="s">
         <v>843</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="36" t="s">
         <v>845</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" s="58" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="36" t="s">
         <v>847</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>849</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="62" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="62" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="36" t="s">
         <v>851</v>
       </c>
@@ -4505,36 +4505,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6EEAB6-D26C-4450-83AD-F740CF51FA1E}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC28"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.296875" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.19921875" style="27" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.69921875" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.19921875" style="27" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="78.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="78.19921875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="80.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="71.69921875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="5" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.19921875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.69921875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.83203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="45.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.796875" style="27" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="45.19921875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.796875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="8" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>637</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46">
         <v>2</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="46">
         <v>3</v>
       </c>
@@ -4817,7 +4817,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="46">
         <v>4</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="46">
         <v>5</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="46">
         <v>6</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="46">
         <v>7</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="46">
         <v>8</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="46">
         <v>9</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="46">
         <v>10</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="46">
         <v>11</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="46">
         <v>12</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="46">
         <v>13</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="46">
         <v>14</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="46">
         <v>15</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="46">
         <v>16</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="46">
         <v>17</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="46">
         <v>18</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="46">
         <v>19</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="46">
         <v>20</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="46">
         <v>21</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="46">
         <v>22</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="46">
         <v>23</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="46">
         <v>24</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="46">
         <v>25</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="46">
         <v>26</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="46">
         <v>27</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="32" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" s="32" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="46">
         <v>28</v>
       </c>
@@ -7156,10 +7156,10 @@
         <v>897</v>
       </c>
       <c r="D28" s="26" t="s">
+        <v>899</v>
+      </c>
+      <c r="E28" s="26" t="s">
         <v>898</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>899</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>900</v>
@@ -7185,11 +7185,11 @@
       </c>
       <c r="M28" s="49" t="str">
         <f t="shared" si="9"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N28" s="49" t="str">
         <f t="shared" si="9"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O28" s="49" t="str">
         <f t="shared" si="9"/>
@@ -7213,11 +7213,11 @@
       </c>
       <c r="U28" s="35" t="str">
         <f t="shared" si="10"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V28" s="50" t="str">
         <f t="shared" si="10"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W28" s="35" t="s">
         <v>705</v>
@@ -7281,13 +7281,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEF6990-269C-482F-AEAB-0F771E87FB19}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>657</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -7434,13 +7434,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56C5A03-15CD-4694-84A2-E149E46D665B}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.83203125" customWidth="1"/>
+    <col min="2" max="3" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="23">
         <v>1</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -7476,44 +7476,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2864B2AC-DDFD-480C-BEC0-F2615FD9637A}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG310"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="43.33203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="43.296875" style="32" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.83203125" customWidth="1"/>
-    <col min="25" max="25" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.83203125" customWidth="1"/>
+    <col min="18" max="18" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.796875" customWidth="1"/>
+    <col min="25" max="25" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.796875" customWidth="1"/>
     <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.83203125" customWidth="1"/>
+    <col min="28" max="28" width="10.796875" customWidth="1"/>
     <col min="29" max="29" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.83203125" customWidth="1"/>
-    <col min="31" max="31" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.83203125" customWidth="1"/>
-    <col min="33" max="33" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.796875" customWidth="1"/>
+    <col min="31" max="31" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.796875" customWidth="1"/>
+    <col min="33" max="33" width="7.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>319</v>
       </c>
@@ -7610,7 +7610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -8519,7 +8519,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="17" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="18" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -9327,7 +9327,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="19" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="20" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -9529,7 +9529,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="21" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -9630,7 +9630,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="22" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -9731,7 +9731,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="23" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="24" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="25" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="26" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="27" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -10236,7 +10236,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="28" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -10337,7 +10337,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="29" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="30" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="31" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -10640,7 +10640,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="32" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -10741,7 +10741,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -11044,7 +11044,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -11246,7 +11246,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -11549,7 +11549,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -11650,7 +11650,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -11751,7 +11751,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -12054,7 +12054,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -12256,7 +12256,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -12357,7 +12357,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="49" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -12458,7 +12458,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="50" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -12559,7 +12559,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="51" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -12660,7 +12660,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="52" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -12761,7 +12761,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="53" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="54" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -12963,7 +12963,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="55" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -13064,7 +13064,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="56" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="57" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -13266,7 +13266,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="58" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -13367,7 +13367,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="59" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -13468,7 +13468,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="60" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="61" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -13670,7 +13670,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="62" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -13771,7 +13771,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="63" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -13872,7 +13872,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="64" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -13973,7 +13973,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -14074,7 +14074,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="66" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -14175,7 +14175,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -14276,7 +14276,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="69" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -14478,7 +14478,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -14579,7 +14579,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="71" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -14680,7 +14680,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="72" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -14781,7 +14781,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -14882,7 +14882,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="74" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -14983,7 +14983,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="75" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -15084,7 +15084,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="76" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -15185,7 +15185,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="77" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -15286,7 +15286,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="78" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -15387,7 +15387,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="79" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -15488,7 +15488,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="80" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -15589,7 +15589,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="81" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -15690,7 +15690,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -15791,7 +15791,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="83" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="85" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -16094,7 +16094,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="86" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -16195,7 +16195,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="87" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="88" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -16397,7 +16397,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="89" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -16498,7 +16498,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="90" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -16599,7 +16599,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="91" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -16700,7 +16700,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="92" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -16801,7 +16801,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="93" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -16902,7 +16902,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="94" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -17003,7 +17003,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="95" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -17104,7 +17104,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="96" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -17205,7 +17205,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -17306,7 +17306,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -17407,7 +17407,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="99" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -17508,7 +17508,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -17609,7 +17609,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -17710,7 +17710,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -17912,7 +17912,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -18013,7 +18013,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -18114,7 +18114,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -18215,7 +18215,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -18316,7 +18316,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -18518,7 +18518,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -18619,7 +18619,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -18720,7 +18720,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="112" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -18821,7 +18821,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -18922,7 +18922,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -19023,7 +19023,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="115" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -19124,7 +19124,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="116" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -19225,7 +19225,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -19326,7 +19326,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="118" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -19427,7 +19427,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="119" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -19528,7 +19528,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -19629,7 +19629,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -19730,7 +19730,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -19831,7 +19831,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -19932,7 +19932,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -20033,7 +20033,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -20134,7 +20134,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -20235,7 +20235,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -20336,7 +20336,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -20437,7 +20437,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="129" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -20538,7 +20538,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="130" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -20639,7 +20639,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="131" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -20740,7 +20740,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="132" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -20841,7 +20841,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="133" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -20942,7 +20942,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -21043,7 +21043,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="135" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="136" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -21245,7 +21245,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="137" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -21346,7 +21346,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="138" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -21447,7 +21447,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="139" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -21548,7 +21548,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="140" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -21649,7 +21649,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="141" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -21750,7 +21750,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="142" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -21851,7 +21851,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="143" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -21952,7 +21952,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="144" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -22053,7 +22053,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="145" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -22154,7 +22154,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="146" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -22255,7 +22255,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="147" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -22356,7 +22356,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="148" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -22457,7 +22457,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="149" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -22558,7 +22558,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="150" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -22659,7 +22659,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="151" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -22760,7 +22760,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="152" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -22861,7 +22861,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="153" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -22962,7 +22962,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="154" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -23063,7 +23063,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="155" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -23164,7 +23164,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="156" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="157" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="9">
         <v>157</v>
       </c>
@@ -23366,7 +23366,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="9">
         <v>158</v>
       </c>
@@ -23467,7 +23467,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="159" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="9">
         <v>159</v>
       </c>
@@ -23568,7 +23568,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="160" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="9">
         <v>160</v>
       </c>
@@ -23669,7 +23669,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="161" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="9">
         <v>161</v>
       </c>
@@ -23770,7 +23770,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="162" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="9">
         <v>162</v>
       </c>
@@ -23871,7 +23871,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="163" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="9">
         <v>163</v>
       </c>
@@ -23972,7 +23972,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="164" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="9">
         <v>164</v>
       </c>
@@ -24073,7 +24073,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="165" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="9">
         <v>165</v>
       </c>
@@ -24174,7 +24174,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="166" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="9">
         <v>166</v>
       </c>
@@ -24275,7 +24275,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="167" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="9">
         <v>167</v>
       </c>
@@ -24376,7 +24376,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="168" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>168</v>
       </c>
@@ -24477,7 +24477,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="169" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="9">
         <v>169</v>
       </c>
@@ -24578,7 +24578,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="170" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="9">
         <v>170</v>
       </c>
@@ -24679,7 +24679,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="171" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="9">
         <v>171</v>
       </c>
@@ -24780,7 +24780,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="172" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="9">
         <v>172</v>
       </c>
@@ -24881,7 +24881,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="173" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="9">
         <v>173</v>
       </c>
@@ -24982,7 +24982,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="174" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="9">
         <v>174</v>
       </c>
@@ -25083,7 +25083,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="175" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="9">
         <v>175</v>
       </c>
@@ -25184,7 +25184,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="176" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="9">
         <v>176</v>
       </c>
@@ -25285,7 +25285,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="177" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="9">
         <v>177</v>
       </c>
@@ -25386,7 +25386,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="178" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="9">
         <v>178</v>
       </c>
@@ -25487,7 +25487,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="179" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="9">
         <v>179</v>
       </c>
@@ -25588,7 +25588,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="180" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="9">
         <v>180</v>
       </c>
@@ -25689,7 +25689,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="181" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="9">
         <v>181</v>
       </c>
@@ -25790,7 +25790,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="182" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="9">
         <v>182</v>
       </c>
@@ -25891,7 +25891,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="183" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="9">
         <v>183</v>
       </c>
@@ -25992,7 +25992,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="9">
         <v>184</v>
       </c>
@@ -26093,7 +26093,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="185" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="9">
         <v>185</v>
       </c>
@@ -26194,7 +26194,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="9">
         <v>186</v>
       </c>
@@ -26295,7 +26295,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="9">
         <v>187</v>
       </c>
@@ -26396,7 +26396,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="188" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="9">
         <v>188</v>
       </c>
@@ -26497,7 +26497,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="189" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="9">
         <v>189</v>
       </c>
@@ -26598,7 +26598,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="190" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="9">
         <v>190</v>
       </c>
@@ -26699,7 +26699,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="191" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="9">
         <v>191</v>
       </c>
@@ -26800,7 +26800,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="192" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="9">
         <v>192</v>
       </c>
@@ -26901,7 +26901,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="193" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="9">
         <v>193</v>
       </c>
@@ -27002,7 +27002,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="194" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="9">
         <v>194</v>
       </c>
@@ -27103,7 +27103,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="195" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="9">
         <v>195</v>
       </c>
@@ -27204,7 +27204,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="196" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="9">
         <v>196</v>
       </c>
@@ -27305,7 +27305,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="197" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="9">
         <v>197</v>
       </c>
@@ -27406,7 +27406,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="198" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="9">
         <v>198</v>
       </c>
@@ -27507,7 +27507,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="199" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="9">
         <v>199</v>
       </c>
@@ -27608,7 +27608,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="200" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="9">
         <v>200</v>
       </c>
@@ -27709,7 +27709,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="201" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="9">
         <v>201</v>
       </c>
@@ -27810,7 +27810,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="202" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="9">
         <v>202</v>
       </c>
@@ -27911,7 +27911,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="203" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="9">
         <v>203</v>
       </c>
@@ -28012,7 +28012,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="204" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="9">
         <v>204</v>
       </c>
@@ -28113,7 +28113,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="205" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="9">
         <v>205</v>
       </c>
@@ -28214,7 +28214,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="206" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="9">
         <v>206</v>
       </c>
@@ -28315,7 +28315,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="207" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="9">
         <v>207</v>
       </c>
@@ -28416,7 +28416,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="208" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="9">
         <v>208</v>
       </c>
@@ -28517,7 +28517,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="209" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="9">
         <v>209</v>
       </c>
@@ -28618,7 +28618,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="210" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="9">
         <v>210</v>
       </c>
@@ -28719,7 +28719,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="211" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="9">
         <v>211</v>
       </c>
@@ -28820,7 +28820,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="212" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="9">
         <v>212</v>
       </c>
@@ -28921,7 +28921,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="213" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="9">
         <v>213</v>
       </c>
@@ -29022,7 +29022,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="214" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="9">
         <v>214</v>
       </c>
@@ -29123,7 +29123,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="215" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="9">
         <v>215</v>
       </c>
@@ -29224,7 +29224,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="216" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="9">
         <v>216</v>
       </c>
@@ -29325,7 +29325,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="217" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="9">
         <v>217</v>
       </c>
@@ -29426,7 +29426,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="218" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="9">
         <v>218</v>
       </c>
@@ -29527,7 +29527,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="219" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="9">
         <v>219</v>
       </c>
@@ -29628,7 +29628,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="220" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="9">
         <v>220</v>
       </c>
@@ -29729,7 +29729,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="221" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="9">
         <v>221</v>
       </c>
@@ -29830,7 +29830,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="222" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="9">
         <v>222</v>
       </c>
@@ -29931,7 +29931,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="223" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="9">
         <v>223</v>
       </c>
@@ -30032,7 +30032,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="224" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="9">
         <v>224</v>
       </c>
@@ -30133,7 +30133,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="225" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="9">
         <v>225</v>
       </c>
@@ -30234,7 +30234,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="226" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="9">
         <v>226</v>
       </c>
@@ -30335,7 +30335,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="227" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="9">
         <v>227</v>
       </c>
@@ -30436,7 +30436,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="228" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="9">
         <v>228</v>
       </c>
@@ -30537,7 +30537,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="229" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="9">
         <v>229</v>
       </c>
@@ -30638,7 +30638,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="230" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="9">
         <v>230</v>
       </c>
@@ -30739,7 +30739,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="231" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="9">
         <v>231</v>
       </c>
@@ -30840,7 +30840,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="232" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="9">
         <v>232</v>
       </c>
@@ -30941,7 +30941,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="233" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="9">
         <v>233</v>
       </c>
@@ -31042,7 +31042,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="234" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="9">
         <v>234</v>
       </c>
@@ -31143,7 +31143,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="235" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="9">
         <v>235</v>
       </c>
@@ -31244,7 +31244,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="236" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="9">
         <v>236</v>
       </c>
@@ -31345,7 +31345,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="237" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="9">
         <v>237</v>
       </c>
@@ -31446,7 +31446,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="238" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="9">
         <v>238</v>
       </c>
@@ -31547,7 +31547,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="239" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="9">
         <v>239</v>
       </c>
@@ -31648,7 +31648,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="240" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="9">
         <v>240</v>
       </c>
@@ -31749,7 +31749,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="241" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="9">
         <v>241</v>
       </c>
@@ -31850,7 +31850,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="242" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="9">
         <v>242</v>
       </c>
@@ -31951,7 +31951,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="243" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="9">
         <v>243</v>
       </c>
@@ -32052,7 +32052,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="244" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="9">
         <v>244</v>
       </c>
@@ -32153,7 +32153,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="245" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="9">
         <v>245</v>
       </c>
@@ -32254,7 +32254,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="246" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="9">
         <v>246</v>
       </c>
@@ -32355,7 +32355,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="247" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="9">
         <v>247</v>
       </c>
@@ -32456,7 +32456,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="9">
         <v>248</v>
       </c>
@@ -32557,7 +32557,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="249" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="9">
         <v>249</v>
       </c>
@@ -32658,7 +32658,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="250" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="9">
         <v>250</v>
       </c>
@@ -32759,7 +32759,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="251" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="9">
         <v>251</v>
       </c>
@@ -32860,7 +32860,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="252" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="9">
         <v>252</v>
       </c>
@@ -32961,7 +32961,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="9">
         <v>253</v>
       </c>
@@ -33062,7 +33062,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="254" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="9">
         <v>254</v>
       </c>
@@ -33163,7 +33163,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="255" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="9">
         <v>255</v>
       </c>
@@ -33264,7 +33264,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="256" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="9">
         <v>256</v>
       </c>
@@ -33365,7 +33365,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="257" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="9">
         <v>257</v>
       </c>
@@ -33466,7 +33466,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="258" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="9">
         <v>258</v>
       </c>
@@ -33567,7 +33567,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="259" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="9">
         <v>259</v>
       </c>
@@ -33668,7 +33668,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="260" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="9">
         <v>260</v>
       </c>
@@ -33769,7 +33769,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="261" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="9">
         <v>261</v>
       </c>
@@ -33870,7 +33870,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="262" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="9">
         <v>262</v>
       </c>
@@ -33971,7 +33971,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="263" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="9">
         <v>263</v>
       </c>
@@ -34072,7 +34072,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="264" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="9">
         <v>264</v>
       </c>
@@ -34173,7 +34173,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="265" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="9">
         <v>265</v>
       </c>
@@ -34274,7 +34274,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="266" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="9">
         <v>266</v>
       </c>
@@ -34375,7 +34375,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="267" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="9">
         <v>267</v>
       </c>
@@ -34476,7 +34476,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="268" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="9">
         <v>268</v>
       </c>
@@ -34577,7 +34577,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="269" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="9">
         <v>269</v>
       </c>
@@ -34678,7 +34678,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="270" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="9">
         <v>270</v>
       </c>
@@ -34779,7 +34779,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="271" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="9">
         <v>271</v>
       </c>
@@ -34880,7 +34880,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="272" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="9">
         <v>272</v>
       </c>
@@ -34981,7 +34981,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="273" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="9">
         <v>273</v>
       </c>
@@ -35082,7 +35082,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="274" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="9">
         <v>274</v>
       </c>
@@ -35183,7 +35183,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="275" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="9">
         <v>275</v>
       </c>
@@ -35284,7 +35284,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="276" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="9">
         <v>276</v>
       </c>
@@ -35385,7 +35385,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="277" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="9">
         <v>277</v>
       </c>
@@ -35486,7 +35486,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="278" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="9">
         <v>278</v>
       </c>
@@ -35587,7 +35587,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="279" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="9">
         <v>279</v>
       </c>
@@ -35688,7 +35688,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="280" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="9">
         <v>280</v>
       </c>
@@ -35789,7 +35789,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="281" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="9">
         <v>281</v>
       </c>
@@ -35890,7 +35890,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="282" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="9">
         <v>282</v>
       </c>
@@ -35991,7 +35991,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="283" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="9">
         <v>283</v>
       </c>
@@ -36092,7 +36092,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="284" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="9">
         <v>284</v>
       </c>
@@ -36193,7 +36193,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="285" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="9">
         <v>285</v>
       </c>
@@ -36294,7 +36294,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="286" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="9">
         <v>286</v>
       </c>
@@ -36395,7 +36395,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="287" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="9">
         <v>287</v>
       </c>
@@ -36496,7 +36496,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="288" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="9">
         <v>288</v>
       </c>
@@ -36597,7 +36597,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="289" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="9">
         <v>289</v>
       </c>
@@ -36698,7 +36698,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="290" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="9">
         <v>290</v>
       </c>
@@ -36799,7 +36799,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="291" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="9">
         <v>291</v>
       </c>
@@ -36900,7 +36900,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="292" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="9">
         <v>292</v>
       </c>
@@ -37001,7 +37001,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="293" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="9">
         <v>293</v>
       </c>
@@ -37102,7 +37102,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="294" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="9">
         <v>294</v>
       </c>
@@ -37203,7 +37203,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="295" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="9">
         <v>295</v>
       </c>
@@ -37304,7 +37304,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="296" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="9">
         <v>296</v>
       </c>
@@ -37405,7 +37405,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="297" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="9">
         <v>297</v>
       </c>
@@ -37506,7 +37506,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="298" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="9">
         <v>298</v>
       </c>
@@ -37607,7 +37607,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="299" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="9">
         <v>299</v>
       </c>
@@ -37708,7 +37708,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="300" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="9">
         <v>300</v>
       </c>
@@ -37809,7 +37809,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="301" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="9">
         <v>301</v>
       </c>
@@ -37910,7 +37910,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="302" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="9">
         <v>302</v>
       </c>
@@ -38011,7 +38011,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="303" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="9">
         <v>303</v>
       </c>
@@ -38112,7 +38112,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="304" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="9">
         <v>304</v>
       </c>
@@ -38213,7 +38213,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="305" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="9">
         <v>305</v>
       </c>
@@ -38314,7 +38314,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="306" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="9">
         <v>306</v>
       </c>
@@ -38416,7 +38416,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="307" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="9">
         <v>307</v>
       </c>
@@ -38518,7 +38518,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="308" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="9">
         <v>308</v>
       </c>
@@ -38620,7 +38620,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="309" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="9">
         <v>309</v>
       </c>
@@ -38722,7 +38722,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="310" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:33" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="9">
         <v>310</v>
       </c>
